--- a/input/reg_wealth_housing.xlsx
+++ b/input/reg_wealth_housing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hrushikeshkalakandra/Documents/GitHub/wealth/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\JAS-MINE\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2110AB1F-E8F7-114B-A9AE-BF2A7216945E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289AC1E8-32FB-4267-858D-4CEB01CF02F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="640" windowWidth="30160" windowHeight="19000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1073" yWindow="1073" windowWidth="14400" windowHeight="8182" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,23 @@
     <sheet name="HW2d" sheetId="10" r:id="rId10"/>
     <sheet name="Auxiliary parameters" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -581,9 +597,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -591,7 +607,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -599,7 +615,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -607,7 +623,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -615,7 +631,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -623,7 +639,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -631,7 +647,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -639,7 +655,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -647,7 +663,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -655,7 +671,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -663,7 +679,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -671,7 +687,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -687,14 +703,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AK36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="37" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -807,7 +823,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -920,7 +936,7 @@
         <v>8.754640795841E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1033,7 +1049,7 @@
         <v>-7.93252307605E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1146,7 +1162,7 @@
         <v>-2.6076779163708499E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1259,7 +1275,7 @@
         <v>-1.33305552124817E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1372,7 +1388,7 @@
         <v>-2.0575654510684E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1485,7 +1501,7 @@
         <v>-7.5160467248611001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1598,7 +1614,7 @@
         <v>-1.43950608690531E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1711,7 +1727,7 @@
         <v>-3.939576701704E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1824,7 +1840,7 @@
         <v>1.2552324925419999E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1937,7 +1953,7 @@
         <v>-2.8115879413850901E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2050,7 +2066,7 @@
         <v>2.6890899923525001E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2163,7 +2179,7 @@
         <v>-2.6711937093485999E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -2276,7 +2292,7 @@
         <v>-2.6308750076219901E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2389,7 +2405,7 @@
         <v>-2.33918194207E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -2502,7 +2518,7 @@
         <v>-3.32524813645491E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -2615,7 +2631,7 @@
         <v>-3.9196341874722103E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2728,7 +2744,7 @@
         <v>-3.3793639334387601E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -2841,7 +2857,7 @@
         <v>-2.9000027317730302E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2954,7 +2970,7 @@
         <v>-7.5854603794498904E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -3067,7 +3083,7 @@
         <v>-2.4588286574596802E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -3180,7 +3196,7 @@
         <v>-2.3270142759061301E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -3293,7 +3309,7 @@
         <v>-2.83031209832104E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -3406,7 +3422,7 @@
         <v>6.9176400508953999E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -3519,7 +3535,7 @@
         <v>-2.5676885269481801E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -3632,7 +3648,7 @@
         <v>-4.0179004808258797E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -3745,7 +3761,7 @@
         <v>-5.1798223726977198E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -3858,7 +3874,7 @@
         <v>-5.11576859077221E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -3971,7 +3987,7 @@
         <v>-3.56477815122841E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -4084,7 +4100,7 @@
         <v>-2.7035347807553602E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -4197,7 +4213,7 @@
         <v>-2.22992205289319E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -4310,7 +4326,7 @@
         <v>-5.78675525710746E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -4423,7 +4439,7 @@
         <v>-3.0706291116462399E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -4536,7 +4552,7 @@
         <v>-2.04689028910084E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -4649,7 +4665,7 @@
         <v>-3.37491344938909E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -4770,7 +4786,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -4778,7 +4794,7 @@
     <col min="4" max="4" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -4792,7 +4808,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -4806,7 +4822,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -4820,7 +4836,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -4834,7 +4850,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -4848,7 +4864,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -4862,7 +4878,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -4876,7 +4892,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -4890,7 +4906,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -4904,7 +4920,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -4926,7 +4942,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -4935,12 +4951,12 @@
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -4957,7 +4973,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -4974,7 +4990,7 @@
         <v>0.2112</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>66</v>
       </c>
@@ -4988,7 +5004,7 @@
         <v>551.63</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -5005,7 +5021,7 @@
         <v>0.1258</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>66</v>
       </c>
@@ -5019,7 +5035,7 @@
         <v>190.75</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -5036,7 +5052,7 @@
         <v>0.58140000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>70</v>
       </c>
@@ -5044,7 +5060,7 @@
         <v>1.05779</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -5061,7 +5077,7 @@
         <v>0.50609999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>70</v>
       </c>
@@ -5072,7 +5088,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>73</v>
       </c>
@@ -5080,7 +5096,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>75</v>
       </c>
@@ -5097,7 +5113,7 @@
         <v>0.62013220999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>66</v>
       </c>
@@ -5111,7 +5127,7 @@
         <v>931.10663</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -5128,7 +5144,7 @@
         <v>0.20102315000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>66</v>
       </c>
@@ -5142,7 +5158,7 @@
         <v>344.73773</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>77</v>
       </c>
@@ -5159,7 +5175,7 @@
         <v>0.28501539999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>70</v>
       </c>
@@ -5173,7 +5189,7 @@
         <v>0.99222343999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>73</v>
       </c>
@@ -5187,7 +5203,7 @@
         <v>0.17344003999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -5204,7 +5220,7 @@
         <v>0.38289127000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>70</v>
       </c>
@@ -5215,7 +5231,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>73</v>
       </c>
@@ -5231,14 +5247,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AJ35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="36" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5348,7 +5364,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>79</v>
       </c>
@@ -5458,7 +5474,7 @@
         <v>-7.1938599036717676E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -5568,7 +5584,7 @@
         <v>-7.7832108704549513E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -5678,7 +5694,7 @@
         <v>-8.2993971369296815E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>80</v>
       </c>
@@ -5788,7 +5804,7 @@
         <v>-8.5680118309014994E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>81</v>
       </c>
@@ -5898,7 +5914,7 @@
         <v>-5.1139111274600392E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>82</v>
       </c>
@@ -6008,7 +6024,7 @@
         <v>-7.8630683143606911E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>83</v>
       </c>
@@ -6118,7 +6134,7 @@
         <v>-1.257587905093306E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>84</v>
       </c>
@@ -6228,7 +6244,7 @@
         <v>5.9265834729542357E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>85</v>
       </c>
@@ -6338,7 +6354,7 @@
         <v>-8.078910256597488E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>86</v>
       </c>
@@ -6448,7 +6464,7 @@
         <v>3.6196702065279169E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -6558,7 +6574,7 @@
         <v>-8.5790615771004445E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -6668,7 +6684,7 @@
         <v>-0.16053628915339771</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -6778,7 +6794,7 @@
         <v>-0.15437887101860581</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -6888,7 +6904,7 @@
         <v>-0.15550150536821419</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -6998,7 +7014,7 @@
         <v>-0.15486015486973631</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -7108,7 +7124,7 @@
         <v>-0.14844910518032189</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -7218,7 +7234,7 @@
         <v>-0.13961626126927459</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -7328,7 +7344,7 @@
         <v>-0.15370236750766719</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -7438,7 +7454,7 @@
         <v>-0.15330020935360589</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -7548,7 +7564,7 @@
         <v>-0.15210722751288799</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -7658,7 +7674,7 @@
         <v>-0.16326052642351291</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -7768,7 +7784,7 @@
         <v>7.7717472889504121E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -7878,7 +7894,7 @@
         <v>-2.4520649554264719E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -7988,7 +8004,7 @@
         <v>-2.3824209425366841E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -8098,7 +8114,7 @@
         <v>-6.4586173292961284E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -8208,7 +8224,7 @@
         <v>-7.1831654788410536E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -8318,7 +8334,7 @@
         <v>-1.8711225899287441E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -8428,7 +8444,7 @@
         <v>-3.7263151852224619E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
@@ -8538,7 +8554,7 @@
         <v>-2.7721500156882722E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -8648,7 +8664,7 @@
         <v>-2.8519443685385851E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
@@ -8758,7 +8774,7 @@
         <v>-3.5809780994223418E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
@@ -8868,7 +8884,7 @@
         <v>-4.098960257168769E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -8978,7 +8994,7 @@
         <v>-2.3339969713130709E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -9096,12 +9112,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AI34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9208,7 +9224,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -9315,7 +9331,7 @@
         <v>-0.24918457445443551</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -9422,7 +9438,7 @@
         <v>-0.28587948822633619</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>80</v>
       </c>
@@ -9529,7 +9545,7 @@
         <v>-0.31784735279964071</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
@@ -9636,7 +9652,7 @@
         <v>-0.24440147972728249</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>82</v>
       </c>
@@ -9743,7 +9759,7 @@
         <v>-0.33064255282334543</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>83</v>
       </c>
@@ -9850,7 +9866,7 @@
         <v>-1.4767247994523379E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>84</v>
       </c>
@@ -9957,7 +9973,7 @@
         <v>-2.7027732158940998E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>85</v>
       </c>
@@ -10064,7 +10080,7 @@
         <v>-1.7990315112062821E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>86</v>
       </c>
@@ -10171,7 +10187,7 @@
         <v>-4.7500518963088769E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -10278,7 +10294,7 @@
         <v>-4.3757131308989207E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -10385,7 +10401,7 @@
         <v>-0.31898492023334402</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -10492,7 +10508,7 @@
         <v>-0.25246623691424308</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -10599,7 +10615,7 @@
         <v>-0.25784525701889938</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -10706,7 +10722,7 @@
         <v>-0.17088518912397879</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -10813,7 +10829,7 @@
         <v>-0.24344870019284531</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -10920,7 +10936,7 @@
         <v>-0.1787876121838185</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
@@ -11027,7 +11043,7 @@
         <v>-0.26176044953585642</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>21</v>
       </c>
@@ -11134,7 +11150,7 @@
         <v>-0.25004334064095413</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>22</v>
       </c>
@@ -11241,7 +11257,7 @@
         <v>-0.26428135673473052</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
@@ -11348,7 +11364,7 @@
         <v>-0.24897860499505031</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -11455,7 +11471,7 @@
         <v>-3.425277907717321E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
@@ -11562,7 +11578,7 @@
         <v>-4.0440634353350137E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -11669,7 +11685,7 @@
         <v>-1.8295044023336031E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
@@ -11776,7 +11792,7 @@
         <v>-5.8054888134557357E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>28</v>
       </c>
@@ -11883,7 +11899,7 @@
         <v>-0.10850385397239611</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -11990,7 +12006,7 @@
         <v>-0.1033970763853421</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
@@ -12097,7 +12113,7 @@
         <v>-7.023413863273488E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>31</v>
       </c>
@@ -12204,7 +12220,7 @@
         <v>-2.8416556847137231E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>32</v>
       </c>
@@ -12311,7 +12327,7 @@
         <v>-5.5468074822217217E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
@@ -12418,7 +12434,7 @@
         <v>1.930934588795896E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
@@ -12525,7 +12541,7 @@
         <v>-4.8945725036581088E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -12632,7 +12648,7 @@
         <v>-6.6744157108954233E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -12747,12 +12763,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AO40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="22" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12877,7 +12893,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
@@ -13002,7 +13018,7 @@
         <v>4.8008746109205374E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -13127,7 +13143,7 @@
         <v>-4.2737434960534143E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>83</v>
       </c>
@@ -13252,7 +13268,7 @@
         <v>-4.1307147338075771E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>84</v>
       </c>
@@ -13377,7 +13393,7 @@
         <v>4.7793862381726022E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
@@ -13502,7 +13518,7 @@
         <v>1.6182688119213221E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -13627,7 +13643,7 @@
         <v>-7.9095761532967682E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -13752,7 +13768,7 @@
         <v>-1.2559846459539171E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -13877,7 +13893,7 @@
         <v>8.9418737413110924E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -14002,7 +14018,7 @@
         <v>7.6540416218992237E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
@@ -14127,7 +14143,7 @@
         <v>2.1037089038110449E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -14252,7 +14268,7 @@
         <v>-1.2666341390893179E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
@@ -14377,7 +14393,7 @@
         <v>-3.7594838984698663E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
@@ -14502,7 +14518,7 @@
         <v>4.6529511658797718E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -14627,7 +14643,7 @@
         <v>-3.7148932679493109E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -14752,7 +14768,7 @@
         <v>8.4647696442054178E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
@@ -14877,7 +14893,7 @@
         <v>-5.0090265885834734E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>80</v>
       </c>
@@ -15002,7 +15018,7 @@
         <v>-1.9499448298157949E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>81</v>
       </c>
@@ -15127,7 +15143,7 @@
         <v>-2.8911600633731041E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>87</v>
       </c>
@@ -15252,7 +15268,7 @@
         <v>-3.7529884100577802E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>88</v>
       </c>
@@ -15377,7 +15393,7 @@
         <v>-2.6042899108527228E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>89</v>
       </c>
@@ -15502,7 +15518,7 @@
         <v>5.6994293253766468E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>90</v>
       </c>
@@ -15627,7 +15643,7 @@
         <v>1.7289038640117781E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
@@ -15752,7 +15768,7 @@
         <v>3.7568074075403421E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -15877,7 +15893,7 @@
         <v>3.0569510606819658E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -16002,7 +16018,7 @@
         <v>8.2358145801205091E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -16127,7 +16143,7 @@
         <v>5.6921556041016053E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -16252,7 +16268,7 @@
         <v>8.2937761910709508E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -16377,7 +16393,7 @@
         <v>7.1150210459148102E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>14</v>
       </c>
@@ -16502,7 +16518,7 @@
         <v>-5.6412624217683119E-6</v>
       </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>15</v>
       </c>
@@ -16627,7 +16643,7 @@
         <v>-3.1760895542850632E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
@@ -16752,7 +16768,7 @@
         <v>4.5383086619841043E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
@@ -16877,7 +16893,7 @@
         <v>-2.5217152986012472E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>18</v>
       </c>
@@ -17002,7 +17018,7 @@
         <v>2.6325849848895849E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -17127,7 +17143,7 @@
         <v>3.3087022913940481E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>20</v>
       </c>
@@ -17252,7 +17268,7 @@
         <v>2.6106471783286442E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>21</v>
       </c>
@@ -17377,7 +17393,7 @@
         <v>6.9174137462376685E-5</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>22</v>
       </c>
@@ -17502,7 +17518,7 @@
         <v>5.5067501710525453E-5</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>23</v>
       </c>
@@ -17627,7 +17643,7 @@
         <v>1.008881259101385E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>91</v>
       </c>
@@ -17760,12 +17776,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AJ35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17875,3744 +17891,3744 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>0.38741717820605431</v>
+        <v>0.73208464349038205</v>
       </c>
       <c r="C2" s="1">
-        <v>1.138166545298056E-2</v>
+        <v>6.7234963365397152E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>2.157155789040752E-2</v>
+        <v>1.2648101296011183E-2</v>
       </c>
       <c r="E2" s="1">
-        <v>2.0663600961393851E-2</v>
+        <v>1.3207619942787324E-3</v>
       </c>
       <c r="F2" s="1">
-        <v>2.3669273904546598E-2</v>
+        <v>5.4270671985474292E-3</v>
       </c>
       <c r="G2" s="1">
-        <v>7.3231644846921849E-3</v>
+        <v>2.6342650992124753E-3</v>
       </c>
       <c r="H2" s="1">
-        <v>-2.74928000127879E-2</v>
+        <v>-1.82964323655678E-3</v>
       </c>
       <c r="I2" s="1">
-        <v>-2.4468350932547862E-2</v>
+        <v>1.5552696559634682E-3</v>
       </c>
       <c r="J2" s="1">
-        <v>-4.2493114053321138E-3</v>
+        <v>-2.4527879147853704E-4</v>
       </c>
       <c r="K2" s="1">
-        <v>4.7614548764489829E-3</v>
+        <v>-1.7218055859576139E-3</v>
       </c>
       <c r="L2" s="1">
-        <v>-1.2532342635736759E-3</v>
+        <v>2.3191404041829483E-3</v>
       </c>
       <c r="M2" s="1">
-        <v>6.815977135787965E-3</v>
+        <v>4.5627716912207891E-4</v>
       </c>
       <c r="N2" s="1">
-        <v>-7.5394414688305655E-2</v>
+        <v>-2.3972603909866268E-5</v>
       </c>
       <c r="O2" s="1">
-        <v>-7.397218930208202E-2</v>
+        <v>2.1942997870389586E-3</v>
       </c>
       <c r="P2" s="1">
-        <v>-4.914236150845782E-2</v>
+        <v>-1.1510480251126394E-3</v>
       </c>
       <c r="Q2" s="1">
-        <v>-5.8880373799092278E-2</v>
+        <v>-6.9001490279459871E-4</v>
       </c>
       <c r="R2" s="1">
-        <v>-4.1613243648053327E-2</v>
+        <v>-1.6755130762337988E-3</v>
       </c>
       <c r="S2" s="1">
-        <v>-6.9521760708652125E-2</v>
+        <v>-8.1341939963453999E-3</v>
       </c>
       <c r="T2" s="1">
-        <v>-6.5923132127371747E-2</v>
+        <v>-8.4058669037446604E-3</v>
       </c>
       <c r="U2" s="1">
-        <v>-5.1485843512042072E-2</v>
+        <v>-1.0425785350725771E-2</v>
       </c>
       <c r="V2" s="1">
-        <v>-5.3444518305808042E-2</v>
+        <v>-1.9315659682025577E-3</v>
       </c>
       <c r="W2" s="1">
-        <v>-4.2130005741966361E-2</v>
+        <v>2.425207913177099E-3</v>
       </c>
       <c r="X2" s="1">
-        <v>1.7891338699478489E-2</v>
+        <v>1.987371725282433E-3</v>
       </c>
       <c r="Y2" s="1">
-        <v>-6.294926834869605E-3</v>
+        <v>-1.5785990061090594E-4</v>
       </c>
       <c r="Z2" s="1">
-        <v>-1.252334927000795E-2</v>
+        <v>-1.3272246129122471E-3</v>
       </c>
       <c r="AA2" s="1">
-        <v>7.8694054560778433E-3</v>
+        <v>-3.2487428993974339E-4</v>
       </c>
       <c r="AB2" s="1">
-        <v>-1.1943973934407491E-2</v>
+        <v>-4.0190504676308747E-3</v>
       </c>
       <c r="AC2" s="1">
-        <v>-9.6373386044443041E-3</v>
+        <v>3.2636442211320576E-3</v>
       </c>
       <c r="AD2" s="1">
-        <v>5.7234287031351482E-4</v>
+        <v>6.6147154844984485E-4</v>
       </c>
       <c r="AE2" s="1">
-        <v>2.630341538207721E-3</v>
+        <v>-2.4600156275379932E-3</v>
       </c>
       <c r="AF2" s="1">
-        <v>-2.1707381376473321E-3</v>
+        <v>-7.2490859582044487E-4</v>
       </c>
       <c r="AG2" s="1">
-        <v>-1.4269800098927841E-3</v>
+        <v>-3.2378118976767699E-3</v>
       </c>
       <c r="AH2" s="1">
-        <v>-2.804134274254173E-2</v>
+        <v>-8.1878829083210092E-3</v>
       </c>
       <c r="AI2" s="1">
-        <v>1.1886379774604111E-2</v>
+        <v>8.3455379649403569E-4</v>
       </c>
       <c r="AJ2" s="1">
-        <v>-7.8270857718464107E-2</v>
+        <v>-8.212449795671567E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>2.717066304313074E-2</v>
+        <v>-0.10773848659691171</v>
       </c>
       <c r="C3" s="1">
-        <v>2.157155789040752E-2</v>
+        <v>1.2648101296011183E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>0.34473040426443119</v>
+        <v>4.3150650269245409E-2</v>
       </c>
       <c r="E3" s="1">
-        <v>0.22700277428051069</v>
+        <v>1.4406653192547147E-2</v>
       </c>
       <c r="F3" s="1">
-        <v>0.20762074238578859</v>
+        <v>1.9274587027326567E-2</v>
       </c>
       <c r="G3" s="1">
-        <v>0.1981194667736732</v>
+        <v>1.6416677041695568E-2</v>
       </c>
       <c r="H3" s="1">
-        <v>4.0208182136505573E-2</v>
+        <v>-6.4251188438389506E-3</v>
       </c>
       <c r="I3" s="1">
-        <v>-0.1939794171336322</v>
+        <v>-4.8025448042898714E-3</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.30033555886690011</v>
+        <v>-1.5492057216536886E-2</v>
       </c>
       <c r="K3" s="1">
-        <v>-9.7318873119857374E-4</v>
+        <v>-6.1936370870579321E-4</v>
       </c>
       <c r="L3" s="1">
-        <v>2.1761312907057299E-2</v>
+        <v>5.8483628579520108E-3</v>
       </c>
       <c r="M3" s="1">
-        <v>-9.6536295214839626E-2</v>
+        <v>-2.342957033352226E-3</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.21142162108056911</v>
+        <v>2.8843081490828593E-3</v>
       </c>
       <c r="O3" s="1">
-        <v>8.1948615588716578E-2</v>
+        <v>7.1347940311505612E-3</v>
       </c>
       <c r="P3" s="1">
-        <v>-7.4518540797262334E-2</v>
+        <v>-5.5324653881337598E-3</v>
       </c>
       <c r="Q3" s="1">
-        <v>-4.8891889482159327E-2</v>
+        <v>-3.1539079890174695E-3</v>
       </c>
       <c r="R3" s="1">
-        <v>0.1268100338036563</v>
+        <v>3.7531930846994447E-3</v>
       </c>
       <c r="S3" s="1">
-        <v>-9.998092919600976E-2</v>
+        <v>-1.490883784501558E-2</v>
       </c>
       <c r="T3" s="1">
-        <v>-7.7688343198040077E-2</v>
+        <v>-3.120327021050856E-2</v>
       </c>
       <c r="U3" s="1">
-        <v>-6.5445432201390541E-2</v>
+        <v>-1.7986150945811116E-2</v>
       </c>
       <c r="V3" s="1">
-        <v>-6.1850141444321598E-2</v>
+        <v>-4.8257949461382385E-3</v>
       </c>
       <c r="W3" s="1">
-        <v>-2.7066879315533528E-2</v>
+        <v>6.3473707479520334E-3</v>
       </c>
       <c r="X3" s="1">
-        <v>2.7146515254906769E-2</v>
+        <v>7.8497002199778287E-3</v>
       </c>
       <c r="Y3" s="1">
-        <v>-8.5165740248448862E-2</v>
+        <v>1.6077794055660974E-3</v>
       </c>
       <c r="Z3" s="1">
-        <v>-1.8524624925212629E-2</v>
+        <v>-2.5432650169475782E-3</v>
       </c>
       <c r="AA3" s="1">
-        <v>7.0725960061235923E-2</v>
+        <v>-2.4077046779181939E-3</v>
       </c>
       <c r="AB3" s="1">
-        <v>5.7654457747829978E-2</v>
+        <v>-1.602180209109838E-2</v>
       </c>
       <c r="AC3" s="1">
-        <v>0.1033298474288723</v>
+        <v>9.8600112319026916E-3</v>
       </c>
       <c r="AD3" s="1">
-        <v>8.2477350755392309E-2</v>
+        <v>5.6670533432064893E-3</v>
       </c>
       <c r="AE3" s="1">
-        <v>1.2180525606093281E-2</v>
+        <v>-5.3027277909500695E-3</v>
       </c>
       <c r="AF3" s="1">
-        <v>3.3917411151228358E-2</v>
+        <v>-9.3289653234714387E-3</v>
       </c>
       <c r="AG3" s="1">
-        <v>2.204091527341745E-2</v>
+        <v>-7.6647083324743667E-3</v>
       </c>
       <c r="AH3" s="1">
-        <v>-7.8460980729351981E-2</v>
+        <v>-1.970254743761532E-2</v>
       </c>
       <c r="AI3" s="1">
-        <v>4.695862102039821E-2</v>
+        <v>-3.7458700000946032E-4</v>
       </c>
       <c r="AJ3" s="1">
-        <v>-0.23530672207505671</v>
+        <v>-0.15456548195816794</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>0.53938869159634395</v>
+        <v>7.6449187275564046E-2</v>
       </c>
       <c r="C4" s="1">
-        <v>2.0663600961393851E-2</v>
+        <v>1.3207619942787324E-3</v>
       </c>
       <c r="D4" s="1">
-        <v>0.22700277428051069</v>
+        <v>1.4406653192547147E-2</v>
       </c>
       <c r="E4" s="1">
-        <v>0.32608663016745337</v>
+        <v>2.1357514091974832E-2</v>
       </c>
       <c r="F4" s="1">
-        <v>0.2288227298089113</v>
+        <v>1.3466810863725323E-2</v>
       </c>
       <c r="G4" s="1">
-        <v>0.21092969347443419</v>
+        <v>1.3178046369342708E-2</v>
       </c>
       <c r="H4" s="1">
-        <v>0.1018686932186216</v>
+        <v>-9.7962317465111748E-3</v>
       </c>
       <c r="I4" s="1">
-        <v>-0.19711831844562949</v>
+        <v>-7.2457792669269848E-3</v>
       </c>
       <c r="J4" s="1">
-        <v>-0.187883980646844</v>
+        <v>-1.3706560249614624E-2</v>
       </c>
       <c r="K4" s="1">
-        <v>6.5380447476493783E-2</v>
+        <v>-1.1603865660725354E-4</v>
       </c>
       <c r="L4" s="1">
-        <v>-1.6691265201792541E-2</v>
+        <v>7.5164327610888204E-4</v>
       </c>
       <c r="M4" s="1">
-        <v>-2.453176468330355E-2</v>
+        <v>-2.8398893663696572E-3</v>
       </c>
       <c r="N4" s="1">
-        <v>-0.19631931865359109</v>
+        <v>3.4053298528674524E-3</v>
       </c>
       <c r="O4" s="1">
-        <v>-0.1754741434202515</v>
+        <v>4.422793119460984E-3</v>
       </c>
       <c r="P4" s="1">
-        <v>-0.1232302618292211</v>
+        <v>-2.053282295838562E-3</v>
       </c>
       <c r="Q4" s="1">
-        <v>-0.1361429877833305</v>
+        <v>-3.7785318126375561E-3</v>
       </c>
       <c r="R4" s="1">
-        <v>7.4304132979337523E-2</v>
+        <v>3.4876058200854054E-3</v>
       </c>
       <c r="S4" s="1">
-        <v>-0.18124981074151031</v>
+        <v>-7.5963552601355372E-3</v>
       </c>
       <c r="T4" s="1">
-        <v>-0.1574828344048689</v>
+        <v>-1.8244558860289806E-2</v>
       </c>
       <c r="U4" s="1">
-        <v>-0.1052582533813384</v>
+        <v>3.1964591492376904E-3</v>
       </c>
       <c r="V4" s="1">
-        <v>-0.12719365433930269</v>
+        <v>-1.347545642570995E-3</v>
       </c>
       <c r="W4" s="1">
-        <v>-0.1012678745251856</v>
+        <v>8.3407179486344723E-4</v>
       </c>
       <c r="X4" s="1">
-        <v>9.4019351970980825E-2</v>
+        <v>5.1842962191385004E-3</v>
       </c>
       <c r="Y4" s="1">
-        <v>2.4937726126294881E-2</v>
+        <v>1.4732560447982945E-3</v>
       </c>
       <c r="Z4" s="1">
-        <v>-6.2236956195012294E-3</v>
+        <v>-2.0076494897728475E-3</v>
       </c>
       <c r="AA4" s="1">
-        <v>-3.9545590440357584E-3</v>
+        <v>-2.6698238092818967E-3</v>
       </c>
       <c r="AB4" s="1">
-        <v>-6.4734131400476569E-2</v>
+        <v>-1.0023852219392032E-2</v>
       </c>
       <c r="AC4" s="1">
-        <v>-6.6158829101653549E-2</v>
+        <v>-2.210950445406621E-4</v>
       </c>
       <c r="AD4" s="1">
-        <v>1.1811030142779501E-3</v>
+        <v>-3.0375730982877547E-3</v>
       </c>
       <c r="AE4" s="1">
-        <v>6.3090251288320728E-4</v>
+        <v>1.9874833144937834E-3</v>
       </c>
       <c r="AF4" s="1">
-        <v>-2.687366437567219E-2</v>
+        <v>-1.3991745868894637E-2</v>
       </c>
       <c r="AG4" s="1">
-        <v>-6.2375510128035777E-3</v>
+        <v>-2.1961956801939964E-3</v>
       </c>
       <c r="AH4" s="1">
-        <v>-7.8239965792529842E-2</v>
+        <v>-3.2923600037883943E-3</v>
       </c>
       <c r="AI4" s="1">
-        <v>1.7825835350572829E-2</v>
+        <v>-4.3321291425609532E-3</v>
       </c>
       <c r="AJ4" s="1">
-        <v>-0.1815310864983295</v>
+        <v>-1.2617962192107535E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>0.30281021366152522</v>
+        <v>-3.7085764021924295E-4</v>
       </c>
       <c r="C5" s="1">
-        <v>2.3669273904546598E-2</v>
+        <v>5.4270671985474292E-3</v>
       </c>
       <c r="D5" s="1">
-        <v>0.20762074238578859</v>
+        <v>1.9274587027326567E-2</v>
       </c>
       <c r="E5" s="1">
-        <v>0.2288227298089113</v>
+        <v>1.3466810863725323E-2</v>
       </c>
       <c r="F5" s="1">
-        <v>0.22796450513018271</v>
+        <v>1.6510954491339658E-2</v>
       </c>
       <c r="G5" s="1">
-        <v>0.1739010195673627</v>
+        <v>1.1946577563645398E-2</v>
       </c>
       <c r="H5" s="1">
-        <v>5.7315504229787227E-2</v>
+        <v>-5.0550632398592768E-3</v>
       </c>
       <c r="I5" s="1">
-        <v>-0.1625400946840766</v>
+        <v>-5.1675712531089896E-3</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.18170053787073709</v>
+        <v>-1.0693082552257135E-2</v>
       </c>
       <c r="K5" s="1">
-        <v>3.2477889299577782E-2</v>
+        <v>-1.7620221614181465E-3</v>
       </c>
       <c r="L5" s="1">
-        <v>-9.1309395793738608E-3</v>
+        <v>1.7454267053894218E-3</v>
       </c>
       <c r="M5" s="1">
-        <v>-3.1058731330510701E-2</v>
+        <v>-9.9774593122121252E-4</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.18394477981318871</v>
+        <v>2.2949779019270657E-3</v>
       </c>
       <c r="O5" s="1">
-        <v>-8.815363862467529E-2</v>
+        <v>4.136704662719308E-3</v>
       </c>
       <c r="P5" s="1">
-        <v>-0.1014702704424644</v>
+        <v>-2.0800345482391049E-3</v>
       </c>
       <c r="Q5" s="1">
-        <v>-0.1161823038586018</v>
+        <v>-2.9452513001808484E-3</v>
       </c>
       <c r="R5" s="1">
-        <v>3.842182093654628E-2</v>
+        <v>4.4477542023793138E-4</v>
       </c>
       <c r="S5" s="1">
-        <v>-0.1461187916211911</v>
+        <v>-9.9967677563315288E-3</v>
       </c>
       <c r="T5" s="1">
-        <v>-0.12871866151818229</v>
+        <v>-1.7837442117422497E-2</v>
       </c>
       <c r="U5" s="1">
-        <v>-8.7698474344865579E-2</v>
+        <v>-5.8432330978372554E-3</v>
       </c>
       <c r="V5" s="1">
-        <v>-8.3819088318361157E-2</v>
+        <v>-2.4144843394310091E-3</v>
       </c>
       <c r="W5" s="1">
-        <v>-8.759753982754874E-2</v>
+        <v>1.7053055047093631E-3</v>
       </c>
       <c r="X5" s="1">
-        <v>6.3725436762151172E-2</v>
+        <v>3.9445589437970864E-3</v>
       </c>
       <c r="Y5" s="1">
-        <v>-2.72419265124971E-2</v>
+        <v>-9.0537028073337834E-5</v>
       </c>
       <c r="Z5" s="1">
-        <v>-5.704049888524132E-4</v>
+        <v>-2.1156575669295796E-3</v>
       </c>
       <c r="AA5" s="1">
-        <v>3.9262907695380232E-2</v>
+        <v>-1.7753436404568147E-3</v>
       </c>
       <c r="AB5" s="1">
-        <v>-9.7211995100152659E-3</v>
+        <v>-8.0469800128721083E-3</v>
       </c>
       <c r="AC5" s="1">
-        <v>-1.8830615865961099E-3</v>
+        <v>2.2336091618963229E-3</v>
       </c>
       <c r="AD5" s="1">
-        <v>6.7320189375223256E-3</v>
+        <v>-1.5572300905417544E-3</v>
       </c>
       <c r="AE5" s="1">
-        <v>1.142164444114295E-2</v>
+        <v>-2.3519820810124735E-3</v>
       </c>
       <c r="AF5" s="1">
-        <v>-1.884594997786692E-2</v>
+        <v>-9.3942656880476802E-3</v>
       </c>
       <c r="AG5" s="1">
-        <v>-1.633818124965598E-2</v>
+        <v>-4.0771470002891504E-3</v>
       </c>
       <c r="AH5" s="1">
-        <v>-7.3588804005110114E-2</v>
+        <v>-8.5575703986695839E-3</v>
       </c>
       <c r="AI5" s="1">
-        <v>4.5252436564171827E-3</v>
+        <v>-3.5748370279422917E-3</v>
       </c>
       <c r="AJ5" s="1">
-        <v>-0.22180643242903469</v>
+        <v>-6.2583426973410072E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>0.37624063376609412</v>
+        <v>0.11329251012965534</v>
       </c>
       <c r="C6" s="1">
-        <v>7.3231644846921849E-3</v>
+        <v>2.6342650992124753E-3</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1981194667736732</v>
+        <v>1.6416677041695568E-2</v>
       </c>
       <c r="E6" s="1">
-        <v>0.21092969347443419</v>
+        <v>1.3178046369342708E-2</v>
       </c>
       <c r="F6" s="1">
-        <v>0.1739010195673627</v>
+        <v>1.1946577563645398E-2</v>
       </c>
       <c r="G6" s="1">
-        <v>0.2308776990161584</v>
+        <v>1.5328763548605301E-2</v>
       </c>
       <c r="H6" s="1">
-        <v>9.2300603181938612E-2</v>
+        <v>-5.3563833629271529E-3</v>
       </c>
       <c r="I6" s="1">
-        <v>-0.14497884599882521</v>
+        <v>-6.0728635464714622E-3</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.19653555782067941</v>
+        <v>-1.28663216431734E-2</v>
       </c>
       <c r="K6" s="1">
-        <v>5.4354409238775853E-2</v>
+        <v>6.6564814671939837E-4</v>
       </c>
       <c r="L6" s="1">
-        <v>-1.3655785779509219E-2</v>
+        <v>1.5599274942378252E-3</v>
       </c>
       <c r="M6" s="1">
-        <v>-2.4596140044109659E-2</v>
+        <v>-1.7755286735582501E-3</v>
       </c>
       <c r="N6" s="1">
-        <v>2.524309540326675E-2</v>
+        <v>5.5206189374661036E-3</v>
       </c>
       <c r="O6" s="1">
-        <v>0.1071062808485095</v>
+        <v>6.8667220766531548E-3</v>
       </c>
       <c r="P6" s="1">
-        <v>7.3959414767419018E-2</v>
+        <v>1.0782840679278427E-4</v>
       </c>
       <c r="Q6" s="1">
-        <v>6.8675192504867755E-2</v>
+        <v>3.9905328715854685E-5</v>
       </c>
       <c r="R6" s="1">
-        <v>0.21619985532652111</v>
+        <v>6.0544565690204711E-3</v>
       </c>
       <c r="S6" s="1">
-        <v>3.4290681219057539E-2</v>
+        <v>-2.9636046908786615E-3</v>
       </c>
       <c r="T6" s="1">
-        <v>4.9486819316468027E-2</v>
+        <v>-1.5608246267423881E-2</v>
       </c>
       <c r="U6" s="1">
-        <v>7.7800167337993553E-2</v>
+        <v>1.5958443510249928E-3</v>
       </c>
       <c r="V6" s="1">
-        <v>6.0823141918332053E-2</v>
+        <v>-2.8718717038291562E-4</v>
       </c>
       <c r="W6" s="1">
-        <v>6.6872262743389033E-2</v>
+        <v>3.2802106681105742E-3</v>
       </c>
       <c r="X6" s="1">
-        <v>6.2645587202907305E-2</v>
+        <v>4.8909201583309907E-3</v>
       </c>
       <c r="Y6" s="1">
-        <v>-7.4716016212980699E-3</v>
+        <v>-2.9478688713022085E-4</v>
       </c>
       <c r="Z6" s="1">
-        <v>-1.9187990188015591E-2</v>
+        <v>-2.476168439548199E-3</v>
       </c>
       <c r="AA6" s="1">
-        <v>-3.6030908663734901E-3</v>
+        <v>-3.7445090522147412E-3</v>
       </c>
       <c r="AB6" s="1">
-        <v>-4.6152807169387418E-2</v>
+        <v>-9.9476277200388624E-3</v>
       </c>
       <c r="AC6" s="1">
-        <v>-3.3928416110938497E-2</v>
+        <v>1.0497823307237635E-3</v>
       </c>
       <c r="AD6" s="1">
-        <v>1.5272554657526371E-2</v>
+        <v>-4.6693465537058637E-4</v>
       </c>
       <c r="AE6" s="1">
-        <v>-2.011618104891064E-2</v>
+        <v>-2.2856855549261111E-3</v>
       </c>
       <c r="AF6" s="1">
-        <v>-2.2441024026501791E-2</v>
+        <v>-1.0543017554580737E-2</v>
       </c>
       <c r="AG6" s="1">
-        <v>-2.3445445531073611E-2</v>
+        <v>-3.3953999051058066E-3</v>
       </c>
       <c r="AH6" s="1">
-        <v>-6.2425361310386063E-2</v>
+        <v>-6.2707635465372447E-3</v>
       </c>
       <c r="AI6" s="1">
-        <v>-7.0724203009400022E-2</v>
+        <v>-5.9208402991956233E-3</v>
       </c>
       <c r="AJ6" s="1">
-        <v>-0.1763764910748834</v>
+        <v>-3.0713017143013888E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.7095676134600597</v>
+        <v>-0.15584389083602498</v>
       </c>
       <c r="C7" s="1">
-        <v>-2.74928000127879E-2</v>
+        <v>-1.82964323655678E-3</v>
       </c>
       <c r="D7" s="1">
-        <v>4.0208182136505573E-2</v>
+        <v>-6.4251188438389506E-3</v>
       </c>
       <c r="E7" s="1">
-        <v>0.1018686932186216</v>
+        <v>-9.7962317465111748E-3</v>
       </c>
       <c r="F7" s="1">
-        <v>5.7315504229787227E-2</v>
+        <v>-5.0550632398592768E-3</v>
       </c>
       <c r="G7" s="1">
-        <v>9.2300603181938612E-2</v>
+        <v>-5.3563833629271529E-3</v>
       </c>
       <c r="H7" s="1">
-        <v>0.57864645642460599</v>
+        <v>3.8269456956567881E-2</v>
       </c>
       <c r="I7" s="1">
-        <v>8.498873052078601E-2</v>
+        <v>-1.64026125213622E-3</v>
       </c>
       <c r="J7" s="1">
-        <v>2.1894049248810329E-2</v>
+        <v>6.5359550002453606E-3</v>
       </c>
       <c r="K7" s="1">
-        <v>0.117764893178329</v>
+        <v>-4.8680356112638587E-4</v>
       </c>
       <c r="L7" s="1">
-        <v>-2.0930710923208199E-2</v>
+        <v>-1.5807137405811937E-3</v>
       </c>
       <c r="M7" s="1">
-        <v>-2.7120087974461531E-3</v>
+        <v>2.9481899546351712E-3</v>
       </c>
       <c r="N7" s="1">
-        <v>0.3333098390607046</v>
+        <v>-3.6163773456415623E-3</v>
       </c>
       <c r="O7" s="1">
-        <v>1.7170632301408251E-2</v>
+        <v>-8.7407657845250657E-3</v>
       </c>
       <c r="P7" s="1">
-        <v>0.1219236594748745</v>
+        <v>3.0878632202620201E-3</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.15431992963960689</v>
+        <v>5.2003438661059383E-3</v>
       </c>
       <c r="R7" s="1">
-        <v>0.17000273039187419</v>
+        <v>4.0202393038123163E-4</v>
       </c>
       <c r="S7" s="1">
-        <v>0.18485600258114451</v>
+        <v>3.2943532964025829E-3</v>
       </c>
       <c r="T7" s="1">
-        <v>0.21323082149834069</v>
+        <v>3.120442396025911E-2</v>
       </c>
       <c r="U7" s="1">
-        <v>0.151593923288071</v>
+        <v>-4.8660188577566571E-3</v>
       </c>
       <c r="V7" s="1">
-        <v>0.16409302625361319</v>
+        <v>4.380982236044063E-4</v>
       </c>
       <c r="W7" s="1">
-        <v>9.698233304195783E-2</v>
+        <v>-9.3394205787343076E-4</v>
       </c>
       <c r="X7" s="1">
-        <v>-6.1852662802893352E-2</v>
+        <v>-7.5208263485289899E-3</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.16276386881078661</v>
+        <v>-3.4231673456802643E-3</v>
       </c>
       <c r="Z7" s="1">
-        <v>0.26785783237521571</v>
+        <v>4.0037630269441661E-3</v>
       </c>
       <c r="AA7" s="1">
-        <v>-1.242018660926412E-2</v>
+        <v>2.1390162896154016E-3</v>
       </c>
       <c r="AB7" s="1">
-        <v>-1.0717405549841959E-2</v>
+        <v>1.2942522400641043E-2</v>
       </c>
       <c r="AC7" s="1">
-        <v>1.118122798890599E-2</v>
+        <v>-3.8530879102744386E-3</v>
       </c>
       <c r="AD7" s="1">
-        <v>-5.304762958926415E-3</v>
+        <v>1.3830130378222668E-3</v>
       </c>
       <c r="AE7" s="1">
-        <v>4.4543546768585629E-2</v>
+        <v>-1.3338804467912871E-3</v>
       </c>
       <c r="AF7" s="1">
-        <v>8.7270134001979111E-2</v>
+        <v>2.2017522976082973E-2</v>
       </c>
       <c r="AG7" s="1">
-        <v>9.1839826104090097E-2</v>
+        <v>4.4064724059021867E-3</v>
       </c>
       <c r="AH7" s="1">
-        <v>0.30691261617536902</v>
+        <v>9.3500937180103494E-3</v>
       </c>
       <c r="AI7" s="1">
-        <v>5.3794750806988999E-2</v>
+        <v>7.3315294708128052E-3</v>
       </c>
       <c r="AJ7" s="1">
-        <v>-0.19315396597978249</v>
+        <v>1.606346913141482E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B8" s="1">
-        <v>-1.0896901338899729</v>
+        <v>1.7944956933508997E-2</v>
       </c>
       <c r="C8" s="1">
-        <v>-2.4468350932547862E-2</v>
+        <v>1.5552696559634682E-3</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.1939794171336322</v>
+        <v>-4.8025448042898714E-3</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.19711831844562949</v>
+        <v>-7.2457792669269848E-3</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.1625400946840766</v>
+        <v>-5.1675712531089896E-3</v>
       </c>
       <c r="G8" s="1">
-        <v>-0.14497884599882521</v>
+        <v>-6.0728635464714622E-3</v>
       </c>
       <c r="H8" s="1">
-        <v>8.498873052078601E-2</v>
+        <v>-1.64026125213622E-3</v>
       </c>
       <c r="I8" s="1">
-        <v>0.32809525351372548</v>
+        <v>1.1812908406991316E-2</v>
       </c>
       <c r="J8" s="1">
-        <v>0.28035359727141068</v>
+        <v>1.2817708464764252E-2</v>
       </c>
       <c r="K8" s="1">
-        <v>3.125676220663579E-3</v>
+        <v>5.5028095184994717E-4</v>
       </c>
       <c r="L8" s="1">
-        <v>-1.064101649338238E-2</v>
+        <v>2.1576559622609598E-4</v>
       </c>
       <c r="M8" s="1">
-        <v>-4.0288863576995841E-3</v>
+        <v>5.8392941605127314E-4</v>
       </c>
       <c r="N8" s="1">
-        <v>0.23035710015893091</v>
+        <v>-2.0531908658362919E-3</v>
       </c>
       <c r="O8" s="1">
-        <v>0.1890947211620452</v>
+        <v>-3.741018935510803E-4</v>
       </c>
       <c r="P8" s="1">
-        <v>0.13185076259083611</v>
+        <v>2.1543055453807458E-3</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.14363325608435221</v>
+        <v>1.0286262449893976E-3</v>
       </c>
       <c r="R8" s="1">
-        <v>5.4895863040315554E-3</v>
+        <v>3.6294302997007721E-4</v>
       </c>
       <c r="S8" s="1">
-        <v>0.19367640994295349</v>
+        <v>-1.3851703386908339E-3</v>
       </c>
       <c r="T8" s="1">
-        <v>0.18375797631164609</v>
+        <v>2.460216779305479E-3</v>
       </c>
       <c r="U8" s="1">
-        <v>0.12940351939227829</v>
+        <v>-4.1292388686491877E-3</v>
       </c>
       <c r="V8" s="1">
-        <v>0.15740075045634791</v>
+        <v>-5.7842615752593928E-4</v>
       </c>
       <c r="W8" s="1">
-        <v>6.5718570044662333E-2</v>
+        <v>4.0465490376796162E-4</v>
       </c>
       <c r="X8" s="1">
-        <v>-9.2814177308577606E-2</v>
+        <v>1.4155144618070541E-4</v>
       </c>
       <c r="Y8" s="1">
-        <v>7.5884026923245945E-2</v>
+        <v>1.0178916322326329E-3</v>
       </c>
       <c r="Z8" s="1">
-        <v>4.9831047279614932E-2</v>
+        <v>-4.1642169312211402E-3</v>
       </c>
       <c r="AA8" s="1">
-        <v>-6.5063588414725537E-2</v>
+        <v>-4.2638508304366643E-3</v>
       </c>
       <c r="AB8" s="1">
-        <v>-2.139522957476063E-2</v>
+        <v>-3.9705436718061498E-3</v>
       </c>
       <c r="AC8" s="1">
-        <v>-2.3022200714247279E-2</v>
+        <v>-5.4888772603512419E-3</v>
       </c>
       <c r="AD8" s="1">
-        <v>-2.5262136109211481E-2</v>
+        <v>-6.8301940960749288E-4</v>
       </c>
       <c r="AE8" s="1">
-        <v>1.2397934509719049E-2</v>
+        <v>-1.3689405567373428E-3</v>
       </c>
       <c r="AF8" s="1">
-        <v>1.878261717032496E-2</v>
+        <v>2.3691409902991036E-3</v>
       </c>
       <c r="AG8" s="1">
-        <v>-4.0499252458409043E-3</v>
+        <v>-2.1730539023692621E-4</v>
       </c>
       <c r="AH8" s="1">
-        <v>0.16085057345829731</v>
+        <v>-1.3784614811090841E-3</v>
       </c>
       <c r="AI8" s="1">
-        <v>1.5224795864045499E-3</v>
+        <v>2.0485760374980332E-3</v>
       </c>
       <c r="AJ8" s="1">
-        <v>3.2955208613743243E-2</v>
+        <v>-2.1325097215286255E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B9" s="1">
-        <v>-0.85434458274058334</v>
+        <v>-2.479725115650416E-2</v>
       </c>
       <c r="C9" s="1">
-        <v>-4.2493114053321138E-3</v>
+        <v>-2.4527879147853704E-4</v>
       </c>
       <c r="D9" s="1">
-        <v>-0.30033555886690011</v>
+        <v>-1.5492057216536886E-2</v>
       </c>
       <c r="E9" s="1">
-        <v>-0.187883980646844</v>
+        <v>-1.3706560249614624E-2</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.18170053787073709</v>
+        <v>-1.0693082552257135E-2</v>
       </c>
       <c r="G9" s="1">
-        <v>-0.19653555782067941</v>
+        <v>-1.28663216431734E-2</v>
       </c>
       <c r="H9" s="1">
-        <v>2.1894049248810329E-2</v>
+        <v>6.5359550002453606E-3</v>
       </c>
       <c r="I9" s="1">
-        <v>0.28035359727141068</v>
+        <v>1.2817708464764252E-2</v>
       </c>
       <c r="J9" s="1">
-        <v>0.49099415885466802</v>
+        <v>2.5297181041025883E-2</v>
       </c>
       <c r="K9" s="1">
-        <v>5.4338310162181748E-2</v>
+        <v>-2.1844842865274693E-3</v>
       </c>
       <c r="L9" s="1">
-        <v>-4.0248577907093228E-2</v>
+        <v>-2.1786340992792511E-3</v>
       </c>
       <c r="M9" s="1">
-        <v>0.1235696413812099</v>
+        <v>3.2863067317312209E-3</v>
       </c>
       <c r="N9" s="1">
-        <v>6.8109066885655961E-2</v>
+        <v>-5.9838099897344798E-3</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.24318522039233409</v>
+        <v>-5.7429617483550043E-3</v>
       </c>
       <c r="P9" s="1">
-        <v>3.5164666397172077E-2</v>
+        <v>3.1593645162432179E-3</v>
       </c>
       <c r="Q9" s="1">
-        <v>-3.9919606483056168E-2</v>
+        <v>1.8074726795125687E-3</v>
       </c>
       <c r="R9" s="1">
-        <v>-0.168664031563214</v>
+        <v>-5.333530401151281E-3</v>
       </c>
       <c r="S9" s="1">
-        <v>-6.77753435110795E-3</v>
+        <v>1.7871081588593865E-3</v>
       </c>
       <c r="T9" s="1">
-        <v>1.787334498133841E-3</v>
+        <v>1.8760186601912109E-2</v>
       </c>
       <c r="U9" s="1">
-        <v>-7.9083359968701306E-3</v>
+        <v>-4.2773598263581604E-3</v>
       </c>
       <c r="V9" s="1">
-        <v>-1.4534471153720471E-2</v>
+        <v>-3.2165849951801793E-4</v>
       </c>
       <c r="W9" s="1">
-        <v>-4.3032434617906713E-2</v>
+        <v>-1.6196735145144045E-3</v>
       </c>
       <c r="X9" s="1">
-        <v>4.9438916956559692E-3</v>
+        <v>-3.8737556235183684E-3</v>
       </c>
       <c r="Y9" s="1">
-        <v>0.1583874895255277</v>
+        <v>5.6792021465732921E-4</v>
       </c>
       <c r="Z9" s="1">
-        <v>3.1850737057619018E-2</v>
+        <v>-2.7655703674008061E-3</v>
       </c>
       <c r="AA9" s="1">
-        <v>-0.1118115359924889</v>
+        <v>-2.4975136293723119E-3</v>
       </c>
       <c r="AB9" s="1">
-        <v>-0.20058060799018179</v>
+        <v>1.4525049168606467E-3</v>
       </c>
       <c r="AC9" s="1">
-        <v>-0.2480509686799173</v>
+        <v>-9.7300677501514221E-3</v>
       </c>
       <c r="AD9" s="1">
-        <v>-7.7918470840034518E-2</v>
+        <v>3.6247816681104356E-5</v>
       </c>
       <c r="AE9" s="1">
-        <v>1.285159387322374E-2</v>
+        <v>1.655937197115603E-3</v>
       </c>
       <c r="AF9" s="1">
-        <v>8.5724139223055974E-3</v>
+        <v>1.1979485823516885E-2</v>
       </c>
       <c r="AG9" s="1">
-        <v>2.788724146944959E-2</v>
+        <v>2.8404846035171554E-3</v>
       </c>
       <c r="AH9" s="1">
-        <v>0.11399840033742439</v>
+        <v>3.9803030710750358E-3</v>
       </c>
       <c r="AI9" s="1">
-        <v>4.555833388385238E-2</v>
+        <v>7.3563671624393527E-3</v>
       </c>
       <c r="AJ9" s="1">
-        <v>-4.225591869591816E-2</v>
+        <v>-4.1117510520252698E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B10" s="1">
-        <v>0.84244118127277345</v>
+        <v>7.2345994638005826E-2</v>
       </c>
       <c r="C10" s="1">
-        <v>4.7614548764489829E-3</v>
+        <v>-1.7218055859576139E-3</v>
       </c>
       <c r="D10" s="1">
-        <v>-9.7318873119857374E-4</v>
+        <v>-6.1936370870579321E-4</v>
       </c>
       <c r="E10" s="1">
-        <v>6.5380447476493783E-2</v>
+        <v>-1.1603865660725354E-4</v>
       </c>
       <c r="F10" s="1">
-        <v>3.2477889299577782E-2</v>
+        <v>-1.7620221614181465E-3</v>
       </c>
       <c r="G10" s="1">
-        <v>5.4354409238775853E-2</v>
+        <v>6.6564814671939837E-4</v>
       </c>
       <c r="H10" s="1">
-        <v>0.117764893178329</v>
+        <v>-4.8680356112638587E-4</v>
       </c>
       <c r="I10" s="1">
-        <v>3.125676220663579E-3</v>
+        <v>5.5028095184994717E-4</v>
       </c>
       <c r="J10" s="1">
-        <v>5.4338310162181748E-2</v>
+        <v>-2.1844842865274693E-3</v>
       </c>
       <c r="K10" s="1">
-        <v>0.29725723631902379</v>
+        <v>7.348100381378851E-3</v>
       </c>
       <c r="L10" s="1">
-        <v>-4.474790706220387E-2</v>
+        <v>-7.3801358464184192E-4</v>
       </c>
       <c r="M10" s="1">
-        <v>5.3052997793887467E-2</v>
+        <v>-1.295184390446397E-3</v>
       </c>
       <c r="N10" s="1">
-        <v>9.7324116644253778E-2</v>
+        <v>1.2036740749129691E-3</v>
       </c>
       <c r="O10" s="1">
-        <v>-0.31354296817973082</v>
+        <v>3.2725515675157725E-4</v>
       </c>
       <c r="P10" s="1">
-        <v>1.2660972522365871E-2</v>
+        <v>9.4516427388284053E-4</v>
       </c>
       <c r="Q10" s="1">
-        <v>-4.6965295621454017E-2</v>
+        <v>-1.8661243977234274E-4</v>
       </c>
       <c r="R10" s="1">
-        <v>5.413805304961572E-2</v>
+        <v>4.1556166536772703E-3</v>
       </c>
       <c r="S10" s="1">
-        <v>-6.5008800736659655E-2</v>
+        <v>3.8726111160216591E-3</v>
       </c>
       <c r="T10" s="1">
-        <v>-4.5173302166005458E-2</v>
+        <v>3.0657778271984265E-4</v>
       </c>
       <c r="U10" s="1">
-        <v>3.0148564232584389E-3</v>
+        <v>2.5412642267028159E-3</v>
       </c>
       <c r="V10" s="1">
-        <v>-5.8887386027943737E-2</v>
+        <v>6.641541740645511E-5</v>
       </c>
       <c r="W10" s="1">
-        <v>-1.165792751147077E-2</v>
+        <v>-6.6679468381931417E-4</v>
       </c>
       <c r="X10" s="1">
-        <v>9.5652601977800358E-2</v>
+        <v>1.0473449405064795E-3</v>
       </c>
       <c r="Y10" s="1">
-        <v>0.2035679021880708</v>
+        <v>3.3405910731248724E-3</v>
       </c>
       <c r="Z10" s="1">
-        <v>6.4806369493712879E-2</v>
+        <v>1.7343053461902165E-3</v>
       </c>
       <c r="AA10" s="1">
-        <v>-5.269424450619839E-2</v>
+        <v>5.1300446736904978E-4</v>
       </c>
       <c r="AB10" s="1">
-        <v>-0.23449003677657829</v>
+        <v>-1.0468728569991322E-3</v>
       </c>
       <c r="AC10" s="1">
-        <v>-0.1908476820643413</v>
+        <v>-2.2142878856084474E-4</v>
       </c>
       <c r="AD10" s="1">
-        <v>6.3849623130647001E-3</v>
+        <v>2.9229449617708785E-3</v>
       </c>
       <c r="AE10" s="1">
-        <v>1.454267234609833E-2</v>
+        <v>4.8530740309433301E-4</v>
       </c>
       <c r="AF10" s="1">
-        <v>3.3009897732817567E-2</v>
+        <v>1.1213940559482577E-4</v>
       </c>
       <c r="AG10" s="1">
-        <v>6.784544712185557E-2</v>
+        <v>1.3276764001764916E-3</v>
       </c>
       <c r="AH10" s="1">
-        <v>5.07046208863558E-2</v>
+        <v>1.9492514316756249E-3</v>
       </c>
       <c r="AI10" s="1">
-        <v>1.9056127654588459E-2</v>
+        <v>-2.7857104302929283E-4</v>
       </c>
       <c r="AJ10" s="1">
-        <v>-0.27386182137797821</v>
+        <v>1.4738992711229054E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="1">
-        <v>-0.15106877573613689</v>
+        <v>-4.7682688730395321E-2</v>
       </c>
       <c r="C11" s="1">
-        <v>-1.2532342635736759E-3</v>
+        <v>2.3191404041829483E-3</v>
       </c>
       <c r="D11" s="1">
-        <v>2.1761312907057299E-2</v>
+        <v>5.8483628579520108E-3</v>
       </c>
       <c r="E11" s="1">
-        <v>-1.6691265201792541E-2</v>
+        <v>7.5164327610888204E-4</v>
       </c>
       <c r="F11" s="1">
-        <v>-9.1309395793738608E-3</v>
+        <v>1.7454267053894218E-3</v>
       </c>
       <c r="G11" s="1">
-        <v>-1.3655785779509219E-2</v>
+        <v>1.5599274942378252E-3</v>
       </c>
       <c r="H11" s="1">
-        <v>-2.0930710923208199E-2</v>
+        <v>-1.5807137405811937E-3</v>
       </c>
       <c r="I11" s="1">
-        <v>-1.064101649338238E-2</v>
+        <v>2.1576559622609598E-4</v>
       </c>
       <c r="J11" s="1">
-        <v>-4.0248577907093228E-2</v>
+        <v>-2.1786340992792511E-3</v>
       </c>
       <c r="K11" s="1">
-        <v>-4.474790706220387E-2</v>
+        <v>-7.3801358464184192E-4</v>
       </c>
       <c r="L11" s="1">
-        <v>2.609475821659113E-2</v>
+        <v>2.2935780214740084E-3</v>
       </c>
       <c r="M11" s="1">
-        <v>-3.160537775437109E-2</v>
+        <v>-1.0551508289759763E-3</v>
       </c>
       <c r="N11" s="1">
-        <v>-1.4360496690049809E-2</v>
+        <v>8.9033167031092088E-4</v>
       </c>
       <c r="O11" s="1">
-        <v>7.3060322616489426E-2</v>
+        <v>2.0428117408070883E-3</v>
       </c>
       <c r="P11" s="1">
-        <v>8.3216855015519915E-3</v>
+        <v>-2.7761430003082422E-4</v>
       </c>
       <c r="Q11" s="1">
-        <v>2.3196426761301001E-2</v>
+        <v>1.9286513377370209E-4</v>
       </c>
       <c r="R11" s="1">
-        <v>1.9193151230736762E-2</v>
+        <v>1.7490454484362674E-3</v>
       </c>
       <c r="S11" s="1">
-        <v>2.821542807069544E-2</v>
+        <v>-2.038391628507876E-3</v>
       </c>
       <c r="T11" s="1">
-        <v>1.491714521699249E-2</v>
+        <v>-6.1258913932471576E-3</v>
       </c>
       <c r="U11" s="1">
-        <v>1.2500165324955679E-2</v>
+        <v>-2.8190727518517221E-3</v>
       </c>
       <c r="V11" s="1">
-        <v>1.770592749990986E-2</v>
+        <v>-4.88150685910512E-4</v>
       </c>
       <c r="W11" s="1">
-        <v>2.5147796553886392E-2</v>
+        <v>1.8475269466701326E-3</v>
       </c>
       <c r="X11" s="1">
-        <v>-2.1199327749214639E-2</v>
+        <v>1.7501963288403988E-3</v>
       </c>
       <c r="Y11" s="1">
-        <v>-4.0083081605852083E-2</v>
+        <v>-7.6966520205565183E-4</v>
       </c>
       <c r="Z11" s="1">
-        <v>-1.529246686459825E-2</v>
+        <v>-9.8392025919412482E-4</v>
       </c>
       <c r="AA11" s="1">
-        <v>1.3246853112916139E-2</v>
+        <v>-1.1734991501480432E-3</v>
       </c>
       <c r="AB11" s="1">
-        <v>4.3491314082666127E-2</v>
+        <v>-3.0040032598688247E-3</v>
       </c>
       <c r="AC11" s="1">
-        <v>5.2457582755240317E-2</v>
+        <v>1.3267683324525278E-3</v>
       </c>
       <c r="AD11" s="1">
-        <v>2.175852007084406E-2</v>
+        <v>1.0991657235865098E-4</v>
       </c>
       <c r="AE11" s="1">
-        <v>9.9869155051263737E-3</v>
+        <v>-1.7009964982481326E-3</v>
       </c>
       <c r="AF11" s="1">
-        <v>1.3658301156641781E-2</v>
+        <v>-1.9261139630739267E-3</v>
       </c>
       <c r="AG11" s="1">
-        <v>1.234576429497752E-2</v>
+        <v>-1.7975829881613577E-3</v>
       </c>
       <c r="AH11" s="1">
-        <v>1.0493768750307381E-3</v>
+        <v>-3.9180553932853836E-3</v>
       </c>
       <c r="AI11" s="1">
-        <v>1.8813261701022072E-2</v>
+        <v>-8.8888660592080482E-4</v>
       </c>
       <c r="AJ11" s="1">
-        <v>2.5991790782175551E-2</v>
+        <v>-2.7625918728394261E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1">
-        <v>0.2953581938277508</v>
+        <v>6.1074230930423468E-2</v>
       </c>
       <c r="C12" s="1">
-        <v>6.815977135787965E-3</v>
+        <v>4.5627716912207891E-4</v>
       </c>
       <c r="D12" s="1">
-        <v>-9.6536295214839626E-2</v>
+        <v>-2.342957033352226E-3</v>
       </c>
       <c r="E12" s="1">
-        <v>-2.453176468330355E-2</v>
+        <v>-2.8398893663696572E-3</v>
       </c>
       <c r="F12" s="1">
-        <v>-3.1058731330510701E-2</v>
+        <v>-9.9774593122121252E-4</v>
       </c>
       <c r="G12" s="1">
-        <v>-2.4596140044109659E-2</v>
+        <v>-1.7755286735582501E-3</v>
       </c>
       <c r="H12" s="1">
-        <v>-2.7120087974461531E-3</v>
+        <v>2.9481899546351712E-3</v>
       </c>
       <c r="I12" s="1">
-        <v>-4.0288863576995841E-3</v>
+        <v>5.8392941605127314E-4</v>
       </c>
       <c r="J12" s="1">
-        <v>0.1235696413812099</v>
+        <v>3.2863067317312209E-3</v>
       </c>
       <c r="K12" s="1">
-        <v>5.3052997793887467E-2</v>
+        <v>-1.295184390446397E-3</v>
       </c>
       <c r="L12" s="1">
-        <v>-3.160537775437109E-2</v>
+        <v>-1.0551508289759763E-3</v>
       </c>
       <c r="M12" s="1">
-        <v>0.1491562225119801</v>
+        <v>4.2038497484421572E-3</v>
       </c>
       <c r="N12" s="1">
-        <v>4.9195449002086E-3</v>
+        <v>-1.3235821448566824E-3</v>
       </c>
       <c r="O12" s="1">
-        <v>-0.28104739719174182</v>
+        <v>-2.4648950074552924E-3</v>
       </c>
       <c r="P12" s="1">
-        <v>-3.118703244540557E-2</v>
+        <v>1.1167466073752489E-4</v>
       </c>
       <c r="Q12" s="1">
-        <v>-7.0292290140131414E-2</v>
+        <v>6.2950909964621759E-5</v>
       </c>
       <c r="R12" s="1">
-        <v>-0.1056058434401921</v>
+        <v>-3.3938357528233518E-3</v>
       </c>
       <c r="S12" s="1">
-        <v>-8.9855432786247982E-2</v>
+        <v>-2.2146332875357172E-3</v>
       </c>
       <c r="T12" s="1">
-        <v>-7.0574154730630959E-2</v>
+        <v>2.942666690323309E-3</v>
       </c>
       <c r="U12" s="1">
-        <v>-4.6131144456501669E-2</v>
+        <v>-1.8776042101888474E-3</v>
       </c>
       <c r="V12" s="1">
-        <v>-7.3883643852360237E-2</v>
+        <v>-1.5790381994389689E-4</v>
       </c>
       <c r="W12" s="1">
-        <v>-1.7552833407507799E-2</v>
+        <v>-2.9182871670569989E-4</v>
       </c>
       <c r="X12" s="1">
-        <v>5.8706632185532508E-2</v>
+        <v>-1.4639154074374745E-3</v>
       </c>
       <c r="Y12" s="1">
-        <v>5.4171348269086511E-2</v>
+        <v>-1.0119355678579164E-4</v>
       </c>
       <c r="Z12" s="1">
-        <v>1.9816755006369619E-2</v>
+        <v>6.9204782809432173E-4</v>
       </c>
       <c r="AA12" s="1">
-        <v>-3.7498264962674221E-2</v>
+        <v>1.1603592097122132E-3</v>
       </c>
       <c r="AB12" s="1">
-        <v>-9.7227761864754791E-2</v>
+        <v>2.6306722155599598E-3</v>
       </c>
       <c r="AC12" s="1">
-        <v>-0.1282237095936157</v>
+        <v>-1.5382695424149425E-3</v>
       </c>
       <c r="AD12" s="1">
-        <v>-8.4871065069188081E-2</v>
+        <v>-1.4156494645343209E-3</v>
       </c>
       <c r="AE12" s="1">
-        <v>-2.5143171476109019E-2</v>
+        <v>-7.0484902597614833E-4</v>
       </c>
       <c r="AF12" s="1">
-        <v>-2.8835533963118921E-2</v>
+        <v>2.9204928497593226E-3</v>
       </c>
       <c r="AG12" s="1">
-        <v>6.1764362147172054E-3</v>
+        <v>-1.8448808312911081E-4</v>
       </c>
       <c r="AH12" s="1">
-        <v>-2.9015787690659711E-2</v>
+        <v>3.5340619446813095E-4</v>
       </c>
       <c r="AI12" s="1">
-        <v>-4.4642552350116251E-2</v>
+        <v>4.2366926769203716E-4</v>
       </c>
       <c r="AJ12" s="1">
-        <v>-1.811092278712478E-2</v>
+        <v>-4.8523576626732616E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1">
-        <v>-2.1850253058302771</v>
+        <v>1.532977983551193E-2</v>
       </c>
       <c r="C13" s="1">
-        <v>-7.5394414688305655E-2</v>
+        <v>-2.3972603909866268E-5</v>
       </c>
       <c r="D13" s="1">
-        <v>-0.21142162108056911</v>
+        <v>2.8843081490828593E-3</v>
       </c>
       <c r="E13" s="1">
-        <v>-0.19631931865359109</v>
+        <v>3.4053298528674524E-3</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.18394477981318871</v>
+        <v>2.2949779019270657E-3</v>
       </c>
       <c r="G13" s="1">
-        <v>2.524309540326675E-2</v>
+        <v>5.5206189374661036E-3</v>
       </c>
       <c r="H13" s="1">
-        <v>0.3333098390607046</v>
+        <v>-3.6163773456415623E-3</v>
       </c>
       <c r="I13" s="1">
-        <v>0.23035710015893091</v>
+        <v>-2.0531908658362919E-3</v>
       </c>
       <c r="J13" s="1">
-        <v>6.8109066885655961E-2</v>
+        <v>-5.9838099897344798E-3</v>
       </c>
       <c r="K13" s="1">
-        <v>9.7324116644253778E-2</v>
+        <v>1.2036740749129691E-3</v>
       </c>
       <c r="L13" s="1">
-        <v>-1.4360496690049809E-2</v>
+        <v>8.9033167031092088E-4</v>
       </c>
       <c r="M13" s="1">
-        <v>4.9195449002086E-3</v>
+        <v>-1.3235821448566824E-3</v>
       </c>
       <c r="N13" s="1">
-        <v>1.9453266420339961</v>
+        <v>8.7321364293471374E-3</v>
       </c>
       <c r="O13" s="1">
-        <v>1.587985124405521</v>
+        <v>6.6706393900914374E-3</v>
       </c>
       <c r="P13" s="1">
-        <v>1.510360288218678</v>
+        <v>3.5231913160211695E-3</v>
       </c>
       <c r="Q13" s="1">
-        <v>1.5573541280595911</v>
+        <v>3.3963427403869567E-3</v>
       </c>
       <c r="R13" s="1">
-        <v>1.3885684453678679</v>
+        <v>6.0231692004728953E-3</v>
       </c>
       <c r="S13" s="1">
-        <v>1.623848693523078</v>
+        <v>4.2186712473436527E-3</v>
       </c>
       <c r="T13" s="1">
-        <v>1.5942614823162411</v>
+        <v>-3.0808034382302507E-3</v>
       </c>
       <c r="U13" s="1">
-        <v>1.537426801479147</v>
+        <v>6.2429477041564263E-3</v>
       </c>
       <c r="V13" s="1">
-        <v>1.5425725245001149</v>
+        <v>3.8316263192561192E-3</v>
       </c>
       <c r="W13" s="1">
-        <v>1.4175382119617419</v>
+        <v>4.1241549275529803E-3</v>
       </c>
       <c r="X13" s="1">
-        <v>-0.1169286202770123</v>
+        <v>1.4894281789131769E-3</v>
       </c>
       <c r="Y13" s="1">
-        <v>0.1086725662816809</v>
+        <v>-1.64191563168317E-3</v>
       </c>
       <c r="Z13" s="1">
-        <v>0.1029910892983512</v>
+        <v>-7.9124273040359627E-4</v>
       </c>
       <c r="AA13" s="1">
-        <v>-0.1008746791087496</v>
+        <v>-2.4613944892730444E-4</v>
       </c>
       <c r="AB13" s="1">
-        <v>-5.4711869501649968E-2</v>
+        <v>-2.9219972655924187E-3</v>
       </c>
       <c r="AC13" s="1">
-        <v>-2.129651796574528E-2</v>
+        <v>9.4021732705720784E-4</v>
       </c>
       <c r="AD13" s="1">
-        <v>-2.892373048335262E-2</v>
+        <v>3.6878157404607315E-5</v>
       </c>
       <c r="AE13" s="1">
-        <v>-5.2427909555444498E-2</v>
+        <v>-1.0654819231160906E-3</v>
       </c>
       <c r="AF13" s="1">
-        <v>-2.9478094841397049E-2</v>
+        <v>-4.7045644829181721E-3</v>
       </c>
       <c r="AG13" s="1">
-        <v>-1.4187386860828041E-2</v>
+        <v>-8.7603846681556796E-4</v>
       </c>
       <c r="AH13" s="1">
-        <v>0.25914974124115853</v>
+        <v>-7.7735987361274295E-4</v>
       </c>
       <c r="AI13" s="1">
-        <v>-0.34362285935060161</v>
+        <v>-4.6855802936645874E-3</v>
       </c>
       <c r="AJ13" s="1">
-        <v>-0.70663520596480733</v>
+        <v>-2.1428645288377179E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="1">
-        <v>-2.661809895772437</v>
+        <v>8.8257646191672156E-3</v>
       </c>
       <c r="C14" s="1">
-        <v>-7.397218930208202E-2</v>
+        <v>2.1942997870389586E-3</v>
       </c>
       <c r="D14" s="1">
-        <v>8.1948615588716578E-2</v>
+        <v>7.1347940311505612E-3</v>
       </c>
       <c r="E14" s="1">
-        <v>-0.1754741434202515</v>
+        <v>4.422793119460984E-3</v>
       </c>
       <c r="F14" s="1">
-        <v>-8.815363862467529E-2</v>
+        <v>4.136704662719308E-3</v>
       </c>
       <c r="G14" s="1">
-        <v>0.1071062808485095</v>
+        <v>6.8667220766531548E-3</v>
       </c>
       <c r="H14" s="1">
-        <v>1.7170632301408251E-2</v>
+        <v>-8.7407657845250657E-3</v>
       </c>
       <c r="I14" s="1">
-        <v>0.1890947211620452</v>
+        <v>-3.741018935510803E-4</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.24318522039233409</v>
+        <v>-5.7429617483550043E-3</v>
       </c>
       <c r="K14" s="1">
-        <v>-0.31354296817973082</v>
+        <v>3.2725515675157725E-4</v>
       </c>
       <c r="L14" s="1">
-        <v>7.3060322616489426E-2</v>
+        <v>2.0428117408070883E-3</v>
       </c>
       <c r="M14" s="1">
-        <v>-0.28104739719174182</v>
+        <v>-2.4648950074552924E-3</v>
       </c>
       <c r="N14" s="1">
-        <v>1.587985124405521</v>
+        <v>6.6706393900914374E-3</v>
       </c>
       <c r="O14" s="1">
-        <v>2.6705184751863991</v>
+        <v>1.2698312705877818E-2</v>
       </c>
       <c r="P14" s="1">
-        <v>1.5727349111823781</v>
+        <v>3.3470897837074923E-3</v>
       </c>
       <c r="Q14" s="1">
-        <v>1.726492651938988</v>
+        <v>3.3168320963489414E-3</v>
       </c>
       <c r="R14" s="1">
-        <v>1.594801989332042</v>
+        <v>7.8963096269349282E-3</v>
       </c>
       <c r="S14" s="1">
-        <v>1.7873218473801069</v>
+        <v>1.9941039022120521E-3</v>
       </c>
       <c r="T14" s="1">
-        <v>1.7566228376982049</v>
+        <v>-8.6808817851430908E-3</v>
       </c>
       <c r="U14" s="1">
-        <v>1.592882841740852</v>
+        <v>4.0972746486747369E-3</v>
       </c>
       <c r="V14" s="1">
-        <v>1.7190681390716609</v>
+        <v>3.7226118713777415E-3</v>
       </c>
       <c r="W14" s="1">
-        <v>1.4776300755047349</v>
+        <v>6.3852639469119035E-3</v>
       </c>
       <c r="X14" s="1">
-        <v>-0.23402520162796911</v>
+        <v>3.7053253756357957E-3</v>
       </c>
       <c r="Y14" s="1">
-        <v>-0.28105512861087911</v>
+        <v>-6.1538957310134854E-4</v>
       </c>
       <c r="Z14" s="1">
-        <v>-9.9331667053556894E-2</v>
+        <v>-2.379680060327502E-3</v>
       </c>
       <c r="AA14" s="1">
-        <v>6.0459501818327432E-2</v>
+        <v>-7.5927318620427897E-4</v>
       </c>
       <c r="AB14" s="1">
-        <v>0.37279351243385811</v>
+        <v>-6.7727835518016644E-3</v>
       </c>
       <c r="AC14" s="1">
-        <v>0.35674610927256772</v>
+        <v>2.2903818695744135E-3</v>
       </c>
       <c r="AD14" s="1">
-        <v>0.1193842375277476</v>
+        <v>-6.6418699222811628E-4</v>
       </c>
       <c r="AE14" s="1">
-        <v>-6.4528370723981807E-2</v>
+        <v>-1.2801243109899774E-3</v>
       </c>
       <c r="AF14" s="1">
-        <v>-6.4807828858669869E-2</v>
+        <v>-7.8903458976185836E-3</v>
       </c>
       <c r="AG14" s="1">
-        <v>-0.16950526014813791</v>
+        <v>-3.4627533623649148E-3</v>
       </c>
       <c r="AH14" s="1">
-        <v>4.7546023568520328E-2</v>
+        <v>-5.9236506907795194E-3</v>
       </c>
       <c r="AI14" s="1">
-        <v>-0.37916023551692662</v>
+        <v>-5.530614335888806E-3</v>
       </c>
       <c r="AJ14" s="1">
-        <v>-0.53565584672363453</v>
+        <v>-2.8856675272554977E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="1">
-        <v>-1.7326420246402461</v>
+        <v>-2.6504731762506589E-2</v>
       </c>
       <c r="C15" s="1">
-        <v>-4.914236150845782E-2</v>
+        <v>-1.1510480251126394E-3</v>
       </c>
       <c r="D15" s="1">
-        <v>-7.4518540797262334E-2</v>
+        <v>-5.5324653881337598E-3</v>
       </c>
       <c r="E15" s="1">
-        <v>-0.1232302618292211</v>
+        <v>-2.053282295838562E-3</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.1014702704424644</v>
+        <v>-2.0800345482391049E-3</v>
       </c>
       <c r="G15" s="1">
-        <v>7.3959414767419018E-2</v>
+        <v>1.0782840679278427E-4</v>
       </c>
       <c r="H15" s="1">
-        <v>0.1219236594748745</v>
+        <v>3.0878632202620201E-3</v>
       </c>
       <c r="I15" s="1">
-        <v>0.13185076259083611</v>
+        <v>2.1543055453807458E-3</v>
       </c>
       <c r="J15" s="1">
-        <v>3.5164666397172077E-2</v>
+        <v>3.1593645162432179E-3</v>
       </c>
       <c r="K15" s="1">
-        <v>1.2660972522365871E-2</v>
+        <v>9.4516427388284053E-4</v>
       </c>
       <c r="L15" s="1">
-        <v>8.3216855015519915E-3</v>
+        <v>-2.7761430003082422E-4</v>
       </c>
       <c r="M15" s="1">
-        <v>-3.118703244540557E-2</v>
+        <v>1.1167466073752489E-4</v>
       </c>
       <c r="N15" s="1">
-        <v>1.510360288218678</v>
+        <v>3.5231913160211695E-3</v>
       </c>
       <c r="O15" s="1">
-        <v>1.5727349111823781</v>
+        <v>3.3470897837074923E-3</v>
       </c>
       <c r="P15" s="1">
-        <v>1.5033780909213801</v>
+        <v>1.3209167310470407E-2</v>
       </c>
       <c r="Q15" s="1">
-        <v>1.440255639825156</v>
+        <v>5.7864445334108588E-3</v>
       </c>
       <c r="R15" s="1">
-        <v>1.3709836581024519</v>
+        <v>2.6620575809950054E-3</v>
       </c>
       <c r="S15" s="1">
-        <v>1.470585845548787</v>
+        <v>5.9812562211411513E-3</v>
       </c>
       <c r="T15" s="1">
-        <v>1.4705718245495121</v>
+        <v>9.6622457852950094E-3</v>
       </c>
       <c r="U15" s="1">
-        <v>1.4222395595676569</v>
+        <v>6.1367511524264007E-3</v>
       </c>
       <c r="V15" s="1">
-        <v>1.417702561578301</v>
+        <v>4.2922272018018279E-3</v>
       </c>
       <c r="W15" s="1">
-        <v>1.351702120191036</v>
+        <v>4.4224017173578115E-3</v>
       </c>
       <c r="X15" s="1">
-        <v>-6.7896656802626687E-2</v>
+        <v>-1.8622224730316245E-3</v>
       </c>
       <c r="Y15" s="1">
-        <v>2.0917510765439129E-5</v>
+        <v>-7.8167788408814269E-4</v>
       </c>
       <c r="Z15" s="1">
-        <v>-3.044953541226714E-2</v>
+        <v>-2.2874269095505481E-3</v>
       </c>
       <c r="AA15" s="1">
-        <v>-4.1669630245641409E-2</v>
+        <v>-9.8910896790193464E-4</v>
       </c>
       <c r="AB15" s="1">
-        <v>-5.5634215489188121E-2</v>
+        <v>5.0260311100938648E-4</v>
       </c>
       <c r="AC15" s="1">
-        <v>-5.5111813428252332E-2</v>
+        <v>-4.9439397674655178E-3</v>
       </c>
       <c r="AD15" s="1">
-        <v>-1.706882875372304E-2</v>
+        <v>-2.2540898047195418E-3</v>
       </c>
       <c r="AE15" s="1">
-        <v>-5.5776238593592382E-2</v>
+        <v>-2.0912026714829113E-3</v>
       </c>
       <c r="AF15" s="1">
-        <v>-2.4539733964498382E-2</v>
+        <v>4.1098700362282026E-3</v>
       </c>
       <c r="AG15" s="1">
-        <v>-1.4471948753321541E-2</v>
+        <v>9.7712573496037958E-4</v>
       </c>
       <c r="AH15" s="1">
-        <v>9.3991909255082273E-2</v>
+        <v>2.8464773306402236E-3</v>
       </c>
       <c r="AI15" s="1">
-        <v>-0.2607523530408532</v>
+        <v>-2.5736466813133796E-4</v>
       </c>
       <c r="AJ15" s="1">
-        <v>-0.79372699276152847</v>
+        <v>9.7026547643392913E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="1">
-        <v>-1.9060630688719939</v>
+        <v>-4.7986689724483222E-2</v>
       </c>
       <c r="C16" s="1">
-        <v>-5.8880373799092278E-2</v>
+        <v>-6.9001490279459871E-4</v>
       </c>
       <c r="D16" s="1">
-        <v>-4.8891889482159327E-2</v>
+        <v>-3.1539079890174695E-3</v>
       </c>
       <c r="E16" s="1">
-        <v>-0.1361429877833305</v>
+        <v>-3.7785318126375561E-3</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.1161823038586018</v>
+        <v>-2.9452513001808484E-3</v>
       </c>
       <c r="G16" s="1">
-        <v>6.8675192504867755E-2</v>
+        <v>3.9905328715854685E-5</v>
       </c>
       <c r="H16" s="1">
-        <v>0.15431992963960689</v>
+        <v>5.2003438661059383E-3</v>
       </c>
       <c r="I16" s="1">
-        <v>0.14363325608435221</v>
+        <v>1.0286262449893976E-3</v>
       </c>
       <c r="J16" s="1">
-        <v>-3.9919606483056168E-2</v>
+        <v>1.8074726795125687E-3</v>
       </c>
       <c r="K16" s="1">
-        <v>-4.6965295621454017E-2</v>
+        <v>-1.8661243977234274E-4</v>
       </c>
       <c r="L16" s="1">
-        <v>2.3196426761301001E-2</v>
+        <v>1.9286513377370209E-4</v>
       </c>
       <c r="M16" s="1">
-        <v>-7.0292290140131414E-2</v>
+        <v>6.2950909964621759E-5</v>
       </c>
       <c r="N16" s="1">
-        <v>1.5573541280595911</v>
+        <v>3.3963427403869567E-3</v>
       </c>
       <c r="O16" s="1">
-        <v>1.726492651938988</v>
+        <v>3.3168320963489414E-3</v>
       </c>
       <c r="P16" s="1">
-        <v>1.440255639825156</v>
+        <v>5.7864445334108588E-3</v>
       </c>
       <c r="Q16" s="1">
-        <v>1.530610047110408</v>
+        <v>9.3956777174549339E-3</v>
       </c>
       <c r="R16" s="1">
-        <v>1.40912568906799</v>
+        <v>3.3719313968616918E-3</v>
       </c>
       <c r="S16" s="1">
-        <v>1.5325261726864909</v>
+        <v>6.8853393596912671E-3</v>
       </c>
       <c r="T16" s="1">
-        <v>1.5214453988321881</v>
+        <v>1.0823033070198385E-2</v>
       </c>
       <c r="U16" s="1">
-        <v>1.4476838307923079</v>
+        <v>5.046171783956277E-3</v>
       </c>
       <c r="V16" s="1">
-        <v>1.4616734022464071</v>
+        <v>4.2409199189312324E-3</v>
       </c>
       <c r="W16" s="1">
-        <v>1.3801495570357469</v>
+        <v>4.3603625615493344E-3</v>
       </c>
       <c r="X16" s="1">
-        <v>-0.1115423584201081</v>
+        <v>-2.7134704066859305E-3</v>
       </c>
       <c r="Y16" s="1">
-        <v>-4.1879884185814682E-2</v>
+        <v>-1.428409148039933E-3</v>
       </c>
       <c r="Z16" s="1">
-        <v>-1.035415697810649E-2</v>
+        <v>-1.1452469130368292E-3</v>
       </c>
       <c r="AA16" s="1">
-        <v>-2.992347081207369E-2</v>
+        <v>2.8978075386659058E-4</v>
       </c>
       <c r="AB16" s="1">
-        <v>5.0259021286431449E-2</v>
+        <v>2.5451472577105727E-3</v>
       </c>
       <c r="AC16" s="1">
-        <v>5.811587804936369E-2</v>
+        <v>-2.3989351535690165E-3</v>
       </c>
       <c r="AD16" s="1">
-        <v>1.9685005994262789E-2</v>
+        <v>-1.0586511528963699E-3</v>
       </c>
       <c r="AE16" s="1">
-        <v>-4.1541439231067873E-2</v>
+        <v>-2.0495463820457555E-3</v>
       </c>
       <c r="AF16" s="1">
-        <v>-4.1400374831276343E-3</v>
+        <v>5.1140522823853451E-3</v>
       </c>
       <c r="AG16" s="1">
-        <v>-9.366277230762235E-3</v>
+        <v>6.9971095446783038E-4</v>
       </c>
       <c r="AH16" s="1">
-        <v>0.11995639215339329</v>
+        <v>1.2409581083864252E-3</v>
       </c>
       <c r="AI16" s="1">
-        <v>-0.25718415642123221</v>
+        <v>1.1701821712986615E-4</v>
       </c>
       <c r="AJ16" s="1">
-        <v>-0.7100526280516215</v>
+        <v>4.5009194893514959E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="1">
-        <v>-0.64215816369107825</v>
+        <v>8.1469057017663563E-2</v>
       </c>
       <c r="C17" s="1">
-        <v>-4.1613243648053327E-2</v>
+        <v>-1.6755130762337988E-3</v>
       </c>
       <c r="D17" s="1">
-        <v>0.1268100338036563</v>
+        <v>3.7531930846994447E-3</v>
       </c>
       <c r="E17" s="1">
-        <v>7.4304132979337523E-2</v>
+        <v>3.4876058200854054E-3</v>
       </c>
       <c r="F17" s="1">
-        <v>3.842182093654628E-2</v>
+        <v>4.4477542023793138E-4</v>
       </c>
       <c r="G17" s="1">
-        <v>0.21619985532652111</v>
+        <v>6.0544565690204711E-3</v>
       </c>
       <c r="H17" s="1">
-        <v>0.17000273039187419</v>
+        <v>4.0202393038123163E-4</v>
       </c>
       <c r="I17" s="1">
-        <v>5.4895863040315554E-3</v>
+        <v>3.6294302997007721E-4</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.168664031563214</v>
+        <v>-5.333530401151281E-3</v>
       </c>
       <c r="K17" s="1">
-        <v>5.413805304961572E-2</v>
+        <v>4.1556166536772703E-3</v>
       </c>
       <c r="L17" s="1">
-        <v>1.9193151230736762E-2</v>
+        <v>1.7490454484362674E-3</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.1056058434401921</v>
+        <v>-3.3938357528233518E-3</v>
       </c>
       <c r="N17" s="1">
-        <v>1.3885684453678679</v>
+        <v>6.0231692004728953E-3</v>
       </c>
       <c r="O17" s="1">
-        <v>1.594801989332042</v>
+        <v>7.8963096269349282E-3</v>
       </c>
       <c r="P17" s="1">
-        <v>1.3709836581024519</v>
+        <v>2.6620575809950054E-3</v>
       </c>
       <c r="Q17" s="1">
-        <v>1.40912568906799</v>
+        <v>3.3719313968616918E-3</v>
       </c>
       <c r="R17" s="1">
-        <v>1.656298437462508</v>
+        <v>2.4703088788215255E-2</v>
       </c>
       <c r="S17" s="1">
-        <v>1.4062892735249219</v>
+        <v>5.3391874059130762E-3</v>
       </c>
       <c r="T17" s="1">
-        <v>1.406870709019872</v>
+        <v>-8.8721242756427676E-3</v>
       </c>
       <c r="U17" s="1">
-        <v>1.4075062837162891</v>
+        <v>6.2663990261365154E-3</v>
       </c>
       <c r="V17" s="1">
-        <v>1.383693954377033</v>
+        <v>3.355639701973924E-3</v>
       </c>
       <c r="W17" s="1">
-        <v>1.3357588736737811</v>
+        <v>5.1233191624353771E-3</v>
       </c>
       <c r="X17" s="1">
-        <v>1.8409215371860022E-2</v>
+        <v>9.0717448952433999E-3</v>
       </c>
       <c r="Y17" s="1">
-        <v>-1.5833507538988659E-2</v>
+        <v>-2.4888534492981899E-3</v>
       </c>
       <c r="Z17" s="1">
-        <v>-4.8724734617202843E-2</v>
+        <v>-1.757459199111279E-3</v>
       </c>
       <c r="AA17" s="1">
-        <v>-4.9843488947988512E-2</v>
+        <v>-4.769868334737512E-3</v>
       </c>
       <c r="AB17" s="1">
-        <v>-8.9546127448600354E-2</v>
+        <v>-1.0765646352698471E-2</v>
       </c>
       <c r="AC17" s="1">
-        <v>-2.1555417308550599E-2</v>
+        <v>-3.6760917863221179E-3</v>
       </c>
       <c r="AD17" s="1">
-        <v>7.6230643299781603E-2</v>
+        <v>1.9406939282684971E-3</v>
       </c>
       <c r="AE17" s="1">
-        <v>-5.2160538451774957E-3</v>
+        <v>7.990413178978889E-4</v>
       </c>
       <c r="AF17" s="1">
-        <v>2.4579123244901639E-3</v>
+        <v>-7.4742924887103712E-3</v>
       </c>
       <c r="AG17" s="1">
-        <v>-3.7762945080939409E-4</v>
+        <v>-1.2558074642224915E-3</v>
       </c>
       <c r="AH17" s="1">
-        <v>1.9536546999857188E-2</v>
+        <v>-1.666189969652121E-3</v>
       </c>
       <c r="AI17" s="1">
-        <v>-0.2249613221918714</v>
+        <v>-4.6420098298437379E-3</v>
       </c>
       <c r="AJ17" s="1">
-        <v>-0.92194857491685855</v>
+        <v>1.4651890529129963E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="1">
-        <v>-1.6959457387274799</v>
+        <v>6.8346086912449699E-2</v>
       </c>
       <c r="C18" s="1">
-        <v>-6.9521760708652125E-2</v>
+        <v>-8.1341939963453999E-3</v>
       </c>
       <c r="D18" s="1">
-        <v>-9.998092919600976E-2</v>
+        <v>-1.490883784501558E-2</v>
       </c>
       <c r="E18" s="1">
-        <v>-0.18124981074151031</v>
+        <v>-7.5963552601355372E-3</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.1461187916211911</v>
+        <v>-9.9967677563315288E-3</v>
       </c>
       <c r="G18" s="1">
-        <v>3.4290681219057539E-2</v>
+        <v>-2.9636046908786615E-3</v>
       </c>
       <c r="H18" s="1">
-        <v>0.18485600258114451</v>
+        <v>3.2943532964025829E-3</v>
       </c>
       <c r="I18" s="1">
-        <v>0.19367640994295349</v>
+        <v>-1.3851703386908339E-3</v>
       </c>
       <c r="J18" s="1">
-        <v>-6.77753435110795E-3</v>
+        <v>1.7871081588593865E-3</v>
       </c>
       <c r="K18" s="1">
-        <v>-6.5008800736659655E-2</v>
+        <v>3.8726111160216591E-3</v>
       </c>
       <c r="L18" s="1">
-        <v>2.821542807069544E-2</v>
+        <v>-2.038391628507876E-3</v>
       </c>
       <c r="M18" s="1">
-        <v>-8.9855432786247982E-2</v>
+        <v>-2.2146332875357172E-3</v>
       </c>
       <c r="N18" s="1">
-        <v>1.623848693523078</v>
+        <v>4.2186712473436527E-3</v>
       </c>
       <c r="O18" s="1">
-        <v>1.7873218473801069</v>
+        <v>1.9941039022120521E-3</v>
       </c>
       <c r="P18" s="1">
-        <v>1.470585845548787</v>
+        <v>5.9812562211411513E-3</v>
       </c>
       <c r="Q18" s="1">
-        <v>1.5325261726864909</v>
+        <v>6.8853393596912671E-3</v>
       </c>
       <c r="R18" s="1">
-        <v>1.4062892735249219</v>
+        <v>5.3391874059130762E-3</v>
       </c>
       <c r="S18" s="1">
-        <v>1.6409084333642661</v>
+        <v>3.1754876804255927E-2</v>
       </c>
       <c r="T18" s="1">
-        <v>1.5767699448306141</v>
+        <v>1.8721567541501227E-2</v>
       </c>
       <c r="U18" s="1">
-        <v>1.4831046920599671</v>
+        <v>1.7456507104861546E-2</v>
       </c>
       <c r="V18" s="1">
-        <v>1.508773667331297</v>
+        <v>6.4244579028180371E-3</v>
       </c>
       <c r="W18" s="1">
-        <v>1.392020700934808</v>
+        <v>1.8748314069350364E-3</v>
       </c>
       <c r="X18" s="1">
-        <v>-0.1540253563350891</v>
+        <v>-5.2949669809034261E-3</v>
       </c>
       <c r="Y18" s="1">
-        <v>-2.2392550138372769E-2</v>
+        <v>6.1539561970100874E-4</v>
       </c>
       <c r="Z18" s="1">
-        <v>1.184444104930937E-2</v>
+        <v>1.6021121126774396E-3</v>
       </c>
       <c r="AA18" s="1">
-        <v>-3.4811615348104397E-2</v>
+        <v>2.2937784364473121E-3</v>
       </c>
       <c r="AB18" s="1">
-        <v>7.4099198054716098E-2</v>
+        <v>6.3904170043979358E-3</v>
       </c>
       <c r="AC18" s="1">
-        <v>8.3136241024189483E-2</v>
+        <v>2.6391449387385552E-5</v>
       </c>
       <c r="AD18" s="1">
-        <v>3.6079963637511037E-2</v>
+        <v>6.6870376208620214E-3</v>
       </c>
       <c r="AE18" s="1">
-        <v>-2.8538916703326062E-2</v>
+        <v>3.0214763491670515E-3</v>
       </c>
       <c r="AF18" s="1">
-        <v>1.077262834543458E-3</v>
+        <v>8.9942347059195904E-3</v>
       </c>
       <c r="AG18" s="1">
-        <v>-1.080602226668788E-2</v>
+        <v>5.8284387990000658E-3</v>
       </c>
       <c r="AH18" s="1">
-        <v>0.1651219428376316</v>
+        <v>9.6649586839266111E-3</v>
       </c>
       <c r="AI18" s="1">
-        <v>-0.24478508177323541</v>
+        <v>2.3437479256150917E-3</v>
       </c>
       <c r="AJ18" s="1">
-        <v>-0.63415478324407992</v>
+        <v>9.049940028705461E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="1">
-        <v>-2.076717768841938</v>
+        <v>-0.12107344144635301</v>
       </c>
       <c r="C19" s="1">
-        <v>-6.5923132127371747E-2</v>
+        <v>-8.4058669037446604E-3</v>
       </c>
       <c r="D19" s="1">
-        <v>-7.7688343198040077E-2</v>
+        <v>-3.120327021050856E-2</v>
       </c>
       <c r="E19" s="1">
-        <v>-0.1574828344048689</v>
+        <v>-1.8244558860289806E-2</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.12871866151818229</v>
+        <v>-1.7837442117422497E-2</v>
       </c>
       <c r="G19" s="1">
-        <v>4.9486819316468027E-2</v>
+        <v>-1.5608246267423881E-2</v>
       </c>
       <c r="H19" s="1">
-        <v>0.21323082149834069</v>
+        <v>3.120442396025911E-2</v>
       </c>
       <c r="I19" s="1">
-        <v>0.18375797631164609</v>
+        <v>2.460216779305479E-3</v>
       </c>
       <c r="J19" s="1">
-        <v>1.787334498133841E-3</v>
+        <v>1.8760186601912109E-2</v>
       </c>
       <c r="K19" s="1">
-        <v>-4.5173302166005458E-2</v>
+        <v>3.0657778271984265E-4</v>
       </c>
       <c r="L19" s="1">
-        <v>1.491714521699249E-2</v>
+        <v>-6.1258913932471576E-3</v>
       </c>
       <c r="M19" s="1">
-        <v>-7.0574154730630959E-2</v>
+        <v>2.942666690323309E-3</v>
       </c>
       <c r="N19" s="1">
-        <v>1.5942614823162411</v>
+        <v>-3.0808034382302507E-3</v>
       </c>
       <c r="O19" s="1">
-        <v>1.7566228376982049</v>
+        <v>-8.6808817851430908E-3</v>
       </c>
       <c r="P19" s="1">
-        <v>1.4705718245495121</v>
+        <v>9.6622457852950094E-3</v>
       </c>
       <c r="Q19" s="1">
-        <v>1.5214453988321881</v>
+        <v>1.0823033070198385E-2</v>
       </c>
       <c r="R19" s="1">
-        <v>1.406870709019872</v>
+        <v>-8.8721242756427676E-3</v>
       </c>
       <c r="S19" s="1">
-        <v>1.5767699448306141</v>
+        <v>1.8721567541501227E-2</v>
       </c>
       <c r="T19" s="1">
-        <v>1.673554225341114</v>
+        <v>7.511210907117255E-2</v>
       </c>
       <c r="U19" s="1">
-        <v>1.4760687110670809</v>
+        <v>9.9958576011448946E-3</v>
       </c>
       <c r="V19" s="1">
-        <v>1.4977257732790861</v>
+        <v>7.8719157420334279E-3</v>
       </c>
       <c r="W19" s="1">
-        <v>1.381877759206632</v>
+        <v>5.520357616206617E-5</v>
       </c>
       <c r="X19" s="1">
-        <v>-0.14807584147940339</v>
+        <v>-1.8976100345427918E-2</v>
       </c>
       <c r="Y19" s="1">
-        <v>-6.5454828488855088E-3</v>
+        <v>-1.1224198680324406E-4</v>
       </c>
       <c r="Z19" s="1">
-        <v>3.3548992081554929E-2</v>
+        <v>5.2651162890981276E-3</v>
       </c>
       <c r="AA19" s="1">
-        <v>-2.0059533657790118E-2</v>
+        <v>8.7175631950267216E-3</v>
       </c>
       <c r="AB19" s="1">
-        <v>6.4293936426133236E-2</v>
+        <v>2.6810153255624358E-2</v>
       </c>
       <c r="AC19" s="1">
-        <v>6.1811022205548238E-2</v>
+        <v>-4.1870805565211583E-3</v>
       </c>
       <c r="AD19" s="1">
-        <v>3.941263185194166E-2</v>
+        <v>1.8700051501530229E-3</v>
       </c>
       <c r="AE19" s="1">
-        <v>1.213817839381892E-2</v>
+        <v>1.0666465039247591E-2</v>
       </c>
       <c r="AF19" s="1">
-        <v>4.7516311303259451E-2</v>
+        <v>3.6892363091133085E-2</v>
       </c>
       <c r="AG19" s="1">
-        <v>1.6219710160822871E-2</v>
+        <v>1.2250506059719293E-2</v>
       </c>
       <c r="AH19" s="1">
-        <v>0.19565988774065349</v>
+        <v>2.2832208666158621E-2</v>
       </c>
       <c r="AI19" s="1">
-        <v>-0.21371418308924239</v>
+        <v>1.4555499644513289E-2</v>
       </c>
       <c r="AJ19" s="1">
-        <v>-0.7218578311102668</v>
+        <v>8.6864156104181411E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="1">
-        <v>-1.403217223145734</v>
+        <v>0.38299423058181009</v>
       </c>
       <c r="C20" s="1">
-        <v>-5.1485843512042072E-2</v>
+        <v>-1.0425785350725771E-2</v>
       </c>
       <c r="D20" s="1">
-        <v>-6.5445432201390541E-2</v>
+        <v>-1.7986150945811116E-2</v>
       </c>
       <c r="E20" s="1">
-        <v>-0.1052582533813384</v>
+        <v>3.1964591492376904E-3</v>
       </c>
       <c r="F20" s="1">
-        <v>-8.7698474344865579E-2</v>
+        <v>-5.8432330978372554E-3</v>
       </c>
       <c r="G20" s="1">
-        <v>7.7800167337993553E-2</v>
+        <v>1.5958443510249928E-3</v>
       </c>
       <c r="H20" s="1">
-        <v>0.151593923288071</v>
+        <v>-4.8660188577566571E-3</v>
       </c>
       <c r="I20" s="1">
-        <v>0.12940351939227829</v>
+        <v>-4.1292388686491877E-3</v>
       </c>
       <c r="J20" s="1">
-        <v>-7.9083359968701306E-3</v>
+        <v>-4.2773598263581604E-3</v>
       </c>
       <c r="K20" s="1">
-        <v>3.0148564232584389E-3</v>
+        <v>2.5412642267028159E-3</v>
       </c>
       <c r="L20" s="1">
-        <v>1.2500165324955679E-2</v>
+        <v>-2.8190727518517221E-3</v>
       </c>
       <c r="M20" s="1">
-        <v>-4.6131144456501669E-2</v>
+        <v>-1.8776042101888474E-3</v>
       </c>
       <c r="N20" s="1">
-        <v>1.537426801479147</v>
+        <v>6.2429477041564263E-3</v>
       </c>
       <c r="O20" s="1">
-        <v>1.592882841740852</v>
+        <v>4.0972746486747369E-3</v>
       </c>
       <c r="P20" s="1">
-        <v>1.4222395595676569</v>
+        <v>6.1367511524264007E-3</v>
       </c>
       <c r="Q20" s="1">
-        <v>1.4476838307923079</v>
+        <v>5.046171783956277E-3</v>
       </c>
       <c r="R20" s="1">
-        <v>1.4075062837162891</v>
+        <v>6.2663990261365154E-3</v>
       </c>
       <c r="S20" s="1">
-        <v>1.4831046920599671</v>
+        <v>1.7456507104861546E-2</v>
       </c>
       <c r="T20" s="1">
-        <v>1.4760687110670809</v>
+        <v>9.9958576011448946E-3</v>
       </c>
       <c r="U20" s="1">
-        <v>1.493927112003508</v>
+        <v>2.8708474979456194E-2</v>
       </c>
       <c r="V20" s="1">
-        <v>1.434608387276898</v>
+        <v>6.8459760599100528E-3</v>
       </c>
       <c r="W20" s="1">
-        <v>1.357784362995009</v>
+        <v>1.2943583007460277E-3</v>
       </c>
       <c r="X20" s="1">
-        <v>-6.0307225052560032E-2</v>
+        <v>-1.9816697780540987E-3</v>
       </c>
       <c r="Y20" s="1">
-        <v>-1.3793407976392171E-2</v>
+        <v>-5.2619039409512389E-4</v>
       </c>
       <c r="Z20" s="1">
-        <v>-2.1612336665595921E-2</v>
+        <v>-1.6501795426561786E-3</v>
       </c>
       <c r="AA20" s="1">
-        <v>-4.842290196857546E-2</v>
+        <v>-6.3860514131400259E-4</v>
       </c>
       <c r="AB20" s="1">
-        <v>-5.0116023934231091E-2</v>
+        <v>1.3390219490333477E-3</v>
       </c>
       <c r="AC20" s="1">
-        <v>-1.841064179989849E-2</v>
+        <v>-6.6076880129388033E-3</v>
       </c>
       <c r="AD20" s="1">
-        <v>8.6186766584949448E-3</v>
+        <v>-2.9942960228746401E-3</v>
       </c>
       <c r="AE20" s="1">
-        <v>-2.0782954332979071E-2</v>
+        <v>2.980144449170552E-3</v>
       </c>
       <c r="AF20" s="1">
-        <v>-1.109825607513182E-2</v>
+        <v>-4.3927491333788093E-3</v>
       </c>
       <c r="AG20" s="1">
-        <v>-4.31472458447206E-3</v>
+        <v>3.8842723260856388E-3</v>
       </c>
       <c r="AH20" s="1">
-        <v>0.1165875439190565</v>
+        <v>1.0586177058758472E-2</v>
       </c>
       <c r="AI20" s="1">
-        <v>-0.2531950933020829</v>
+        <v>-5.3780525967735554E-3</v>
       </c>
       <c r="AJ20" s="1">
-        <v>-0.79308059445831791</v>
+        <v>0.12710133808296287</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="1">
-        <v>-1.7914968989982449</v>
+        <v>0.14839104154799465</v>
       </c>
       <c r="C21" s="1">
-        <v>-5.3444518305808042E-2</v>
+        <v>-1.9315659682025577E-3</v>
       </c>
       <c r="D21" s="1">
-        <v>-6.1850141444321598E-2</v>
+        <v>-4.8257949461382385E-3</v>
       </c>
       <c r="E21" s="1">
-        <v>-0.12719365433930269</v>
+        <v>-1.347545642570995E-3</v>
       </c>
       <c r="F21" s="1">
-        <v>-8.3819088318361157E-2</v>
+        <v>-2.4144843394310091E-3</v>
       </c>
       <c r="G21" s="1">
-        <v>6.0823141918332053E-2</v>
+        <v>-2.8718717038291562E-4</v>
       </c>
       <c r="H21" s="1">
-        <v>0.16409302625361319</v>
+        <v>4.380982236044063E-4</v>
       </c>
       <c r="I21" s="1">
-        <v>0.15740075045634791</v>
+        <v>-5.7842615752593928E-4</v>
       </c>
       <c r="J21" s="1">
-        <v>-1.4534471153720471E-2</v>
+        <v>-3.2165849951801793E-4</v>
       </c>
       <c r="K21" s="1">
-        <v>-5.8887386027943737E-2</v>
+        <v>6.641541740645511E-5</v>
       </c>
       <c r="L21" s="1">
-        <v>1.770592749990986E-2</v>
+        <v>-4.88150685910512E-4</v>
       </c>
       <c r="M21" s="1">
-        <v>-7.3883643852360237E-2</v>
+        <v>-1.5790381994389689E-4</v>
       </c>
       <c r="N21" s="1">
-        <v>1.5425725245001149</v>
+        <v>3.8316263192561192E-3</v>
       </c>
       <c r="O21" s="1">
-        <v>1.7190681390716609</v>
+        <v>3.7226118713777415E-3</v>
       </c>
       <c r="P21" s="1">
-        <v>1.417702561578301</v>
+        <v>4.2922272018018279E-3</v>
       </c>
       <c r="Q21" s="1">
-        <v>1.4616734022464071</v>
+        <v>4.2409199189312324E-3</v>
       </c>
       <c r="R21" s="1">
-        <v>1.383693954377033</v>
+        <v>3.355639701973924E-3</v>
       </c>
       <c r="S21" s="1">
-        <v>1.508773667331297</v>
+        <v>6.4244579028180371E-3</v>
       </c>
       <c r="T21" s="1">
-        <v>1.4977257732790861</v>
+        <v>7.8719157420334279E-3</v>
       </c>
       <c r="U21" s="1">
-        <v>1.434608387276898</v>
+        <v>6.8459760599100528E-3</v>
       </c>
       <c r="V21" s="1">
-        <v>1.517259747152607</v>
+        <v>1.0195563008963709E-2</v>
       </c>
       <c r="W21" s="1">
-        <v>1.3431616804000099</v>
+        <v>3.1721731302925028E-3</v>
       </c>
       <c r="X21" s="1">
-        <v>-0.1079709806076965</v>
+        <v>-1.4452654286285366E-3</v>
       </c>
       <c r="Y21" s="1">
-        <v>-4.885596744160331E-2</v>
+        <v>-8.3100201282312186E-4</v>
       </c>
       <c r="Z21" s="1">
-        <v>1.1924855021535291E-2</v>
+        <v>1.0388365469483629E-3</v>
       </c>
       <c r="AA21" s="1">
-        <v>-3.656541171883632E-3</v>
+        <v>3.2126117483656652E-3</v>
       </c>
       <c r="AB21" s="1">
-        <v>5.9557322080621811E-2</v>
+        <v>3.9763277652014317E-3</v>
       </c>
       <c r="AC21" s="1">
-        <v>7.1381626679946075E-2</v>
+        <v>5.3791021107371662E-4</v>
       </c>
       <c r="AD21" s="1">
-        <v>1.446823903934533E-2</v>
+        <v>-2.6480092218950091E-5</v>
       </c>
       <c r="AE21" s="1">
-        <v>-2.082377716608351E-2</v>
+        <v>1.9288124436450671E-3</v>
       </c>
       <c r="AF21" s="1">
-        <v>-2.416969939227176E-2</v>
+        <v>2.1061930469779E-3</v>
       </c>
       <c r="AG21" s="1">
-        <v>-3.5660326873474812E-2</v>
+        <v>2.0115787061199264E-4</v>
       </c>
       <c r="AH21" s="1">
-        <v>0.1293093951997015</v>
+        <v>4.0878655532931019E-3</v>
       </c>
       <c r="AI21" s="1">
-        <v>-0.2608682137584154</v>
+        <v>-5.3310191419034259E-5</v>
       </c>
       <c r="AJ21" s="1">
-        <v>-0.77830574819028975</v>
+        <v>1.836431512714598E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="1">
-        <v>-1.528460706049994</v>
+        <v>-9.3141311917113376E-2</v>
       </c>
       <c r="C22" s="1">
-        <v>-4.2130005741966361E-2</v>
+        <v>2.425207913177099E-3</v>
       </c>
       <c r="D22" s="1">
-        <v>-2.7066879315533528E-2</v>
+        <v>6.3473707479520334E-3</v>
       </c>
       <c r="E22" s="1">
-        <v>-0.1012678745251856</v>
+        <v>8.3407179486344723E-4</v>
       </c>
       <c r="F22" s="1">
-        <v>-8.759753982754874E-2</v>
+        <v>1.7053055047093631E-3</v>
       </c>
       <c r="G22" s="1">
-        <v>6.6872262743389033E-2</v>
+        <v>3.2802106681105742E-3</v>
       </c>
       <c r="H22" s="1">
-        <v>9.698233304195783E-2</v>
+        <v>-9.3394205787343076E-4</v>
       </c>
       <c r="I22" s="1">
-        <v>6.5718570044662333E-2</v>
+        <v>4.0465490376796162E-4</v>
       </c>
       <c r="J22" s="1">
-        <v>-4.3032434617906713E-2</v>
+        <v>-1.6196735145144045E-3</v>
       </c>
       <c r="K22" s="1">
-        <v>-1.165792751147077E-2</v>
+        <v>-6.6679468381931417E-4</v>
       </c>
       <c r="L22" s="1">
-        <v>2.5147796553886392E-2</v>
+        <v>1.8475269466701326E-3</v>
       </c>
       <c r="M22" s="1">
-        <v>-1.7552833407507799E-2</v>
+        <v>-2.9182871670569989E-4</v>
       </c>
       <c r="N22" s="1">
-        <v>1.4175382119617419</v>
+        <v>4.1241549275529803E-3</v>
       </c>
       <c r="O22" s="1">
-        <v>1.4776300755047349</v>
+        <v>6.3852639469119035E-3</v>
       </c>
       <c r="P22" s="1">
-        <v>1.351702120191036</v>
+        <v>4.4224017173578115E-3</v>
       </c>
       <c r="Q22" s="1">
-        <v>1.3801495570357469</v>
+        <v>4.3603625615493344E-3</v>
       </c>
       <c r="R22" s="1">
-        <v>1.3357588736737811</v>
+        <v>5.1233191624353771E-3</v>
       </c>
       <c r="S22" s="1">
-        <v>1.392020700934808</v>
+        <v>1.8748314069350364E-3</v>
       </c>
       <c r="T22" s="1">
-        <v>1.381877759206632</v>
+        <v>5.520357616206617E-5</v>
       </c>
       <c r="U22" s="1">
-        <v>1.357784362995009</v>
+        <v>1.2943583007460277E-3</v>
       </c>
       <c r="V22" s="1">
-        <v>1.3431616804000099</v>
+        <v>3.1721731302925028E-3</v>
       </c>
       <c r="W22" s="1">
-        <v>1.374003977179898</v>
+        <v>1.2081540785299829E-2</v>
       </c>
       <c r="X22" s="1">
-        <v>-5.4124174005512497E-2</v>
+        <v>6.8541527446400186E-4</v>
       </c>
       <c r="Y22" s="1">
-        <v>-4.1477886583184909E-2</v>
+        <v>1.2524388977793247E-4</v>
       </c>
       <c r="Z22" s="1">
-        <v>-3.308873099386378E-2</v>
+        <v>-2.2596607626433618E-3</v>
       </c>
       <c r="AA22" s="1">
-        <v>-3.2064715871190419E-2</v>
+        <v>8.0185380917747323E-4</v>
       </c>
       <c r="AB22" s="1">
-        <v>-1.0140289045093681E-2</v>
+        <v>-3.5942009547263731E-3</v>
       </c>
       <c r="AC22" s="1">
-        <v>1.0247861719041461E-2</v>
+        <v>1.1092501836849067E-3</v>
       </c>
       <c r="AD22" s="1">
-        <v>-1.363409448500136E-3</v>
+        <v>-6.5330046727028745E-4</v>
       </c>
       <c r="AE22" s="1">
-        <v>-3.3446217676563791E-2</v>
+        <v>-4.8705202788484891E-4</v>
       </c>
       <c r="AF22" s="1">
-        <v>-4.2141315406689639E-3</v>
+        <v>4.1448575929914355E-5</v>
       </c>
       <c r="AG22" s="1">
-        <v>3.0816319005545781E-2</v>
+        <v>-1.7354099892290392E-3</v>
       </c>
       <c r="AH22" s="1">
-        <v>5.6656058473455007E-2</v>
+        <v>-3.7619694717319629E-3</v>
       </c>
       <c r="AI22" s="1">
-        <v>-0.22685083804772591</v>
+        <v>-3.0050642498025137E-4</v>
       </c>
       <c r="AJ22" s="1">
-        <v>-0.79304829728323867</v>
+        <v>-3.3742848828749672E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="1">
-        <v>0.9416898755349763</v>
+        <v>0.13290212767953805</v>
       </c>
       <c r="C23" s="1">
-        <v>1.7891338699478489E-2</v>
+        <v>1.987371725282433E-3</v>
       </c>
       <c r="D23" s="1">
-        <v>2.7146515254906769E-2</v>
+        <v>7.8497002199778287E-3</v>
       </c>
       <c r="E23" s="1">
-        <v>9.4019351970980825E-2</v>
+        <v>5.1842962191385004E-3</v>
       </c>
       <c r="F23" s="1">
-        <v>6.3725436762151172E-2</v>
+        <v>3.9445589437970864E-3</v>
       </c>
       <c r="G23" s="1">
-        <v>6.2645587202907305E-2</v>
+        <v>4.8909201583309907E-3</v>
       </c>
       <c r="H23" s="1">
-        <v>-6.1852662802893352E-2</v>
+        <v>-7.5208263485289899E-3</v>
       </c>
       <c r="I23" s="1">
-        <v>-9.2814177308577606E-2</v>
+        <v>1.4155144618070541E-4</v>
       </c>
       <c r="J23" s="1">
-        <v>4.9438916956559692E-3</v>
+        <v>-3.8737556235183684E-3</v>
       </c>
       <c r="K23" s="1">
-        <v>9.5652601977800358E-2</v>
+        <v>1.0473449405064795E-3</v>
       </c>
       <c r="L23" s="1">
-        <v>-2.1199327749214639E-2</v>
+        <v>1.7501963288403988E-3</v>
       </c>
       <c r="M23" s="1">
-        <v>5.8706632185532508E-2</v>
+        <v>-1.4639154074374745E-3</v>
       </c>
       <c r="N23" s="1">
-        <v>-0.1169286202770123</v>
+        <v>1.4894281789131769E-3</v>
       </c>
       <c r="O23" s="1">
-        <v>-0.23402520162796911</v>
+        <v>3.7053253756357957E-3</v>
       </c>
       <c r="P23" s="1">
-        <v>-6.7896656802626687E-2</v>
+        <v>-1.8622224730316245E-3</v>
       </c>
       <c r="Q23" s="1">
-        <v>-0.1115423584201081</v>
+        <v>-2.7134704066859305E-3</v>
       </c>
       <c r="R23" s="1">
-        <v>1.8409215371860022E-2</v>
+        <v>9.0717448952433999E-3</v>
       </c>
       <c r="S23" s="1">
-        <v>-0.1540253563350891</v>
+        <v>-5.2949669809034261E-3</v>
       </c>
       <c r="T23" s="1">
-        <v>-0.14807584147940339</v>
+        <v>-1.8976100345427918E-2</v>
       </c>
       <c r="U23" s="1">
-        <v>-6.0307225052560032E-2</v>
+        <v>-1.9816697780540987E-3</v>
       </c>
       <c r="V23" s="1">
-        <v>-0.1079709806076965</v>
+        <v>-1.4452654286285366E-3</v>
       </c>
       <c r="W23" s="1">
-        <v>-5.4124174005512497E-2</v>
+        <v>6.8541527446400186E-4</v>
       </c>
       <c r="X23" s="1">
-        <v>0.14914084932935329</v>
+        <v>1.0648150045277931E-2</v>
       </c>
       <c r="Y23" s="1">
-        <v>3.0431417651178488E-2</v>
+        <v>-1.6407986389393495E-3</v>
       </c>
       <c r="Z23" s="1">
-        <v>-5.2536173860719473E-2</v>
+        <v>-2.5787145194650272E-3</v>
       </c>
       <c r="AA23" s="1">
-        <v>-3.92826521172292E-2</v>
+        <v>-5.485377876734799E-3</v>
       </c>
       <c r="AB23" s="1">
-        <v>-0.16301382573154091</v>
+        <v>-1.2413995084986815E-2</v>
       </c>
       <c r="AC23" s="1">
-        <v>-0.15790694804321409</v>
+        <v>-2.0436933254905153E-3</v>
       </c>
       <c r="AD23" s="1">
-        <v>-1.6876516050397871E-2</v>
+        <v>7.8346174502820585E-4</v>
       </c>
       <c r="AE23" s="1">
-        <v>-1.0062031867711631E-2</v>
+        <v>-1.1181121633983097E-3</v>
       </c>
       <c r="AF23" s="1">
-        <v>-3.5785121981088297E-2</v>
+        <v>-1.1061729321517964E-2</v>
       </c>
       <c r="AG23" s="1">
-        <v>-1.2578098641603931E-2</v>
+        <v>-3.2671275593396491E-3</v>
       </c>
       <c r="AH23" s="1">
-        <v>-0.10518534027886681</v>
+        <v>-6.2469103479201871E-3</v>
       </c>
       <c r="AI23" s="1">
-        <v>-3.4747191143682153E-2</v>
+        <v>-4.734312758234392E-3</v>
       </c>
       <c r="AJ23" s="1">
-        <v>-0.1203094589467008</v>
+        <v>-2.1858999802256605E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B24" s="1">
-        <v>-0.1171937509003833</v>
+        <v>1.2965568771758114E-2</v>
       </c>
       <c r="C24" s="1">
-        <v>-6.294926834869605E-3</v>
+        <v>-1.5785990061090594E-4</v>
       </c>
       <c r="D24" s="1">
-        <v>-8.5165740248448862E-2</v>
+        <v>1.6077794055660974E-3</v>
       </c>
       <c r="E24" s="1">
-        <v>2.4937726126294881E-2</v>
+        <v>1.4732560447982945E-3</v>
       </c>
       <c r="F24" s="1">
-        <v>-2.72419265124971E-2</v>
+        <v>-9.0537028073337834E-5</v>
       </c>
       <c r="G24" s="1">
-        <v>-7.4716016212980699E-3</v>
+        <v>-2.9478688713022085E-4</v>
       </c>
       <c r="H24" s="1">
-        <v>0.16276386881078661</v>
+        <v>-3.4231673456802643E-3</v>
       </c>
       <c r="I24" s="1">
-        <v>7.5884026923245945E-2</v>
+        <v>1.0178916322326329E-3</v>
       </c>
       <c r="J24" s="1">
-        <v>0.1583874895255277</v>
+        <v>5.6792021465732921E-4</v>
       </c>
       <c r="K24" s="1">
-        <v>0.2035679021880708</v>
+        <v>3.3405910731248724E-3</v>
       </c>
       <c r="L24" s="1">
-        <v>-4.0083081605852083E-2</v>
+        <v>-7.6966520205565183E-4</v>
       </c>
       <c r="M24" s="1">
-        <v>5.4171348269086511E-2</v>
+        <v>-1.0119355678579164E-4</v>
       </c>
       <c r="N24" s="1">
-        <v>0.1086725662816809</v>
+        <v>-1.64191563168317E-3</v>
       </c>
       <c r="O24" s="1">
-        <v>-0.28105512861087911</v>
+        <v>-6.1538957310134854E-4</v>
       </c>
       <c r="P24" s="1">
-        <v>2.0917510765439129E-5</v>
+        <v>-7.8167788408814269E-4</v>
       </c>
       <c r="Q24" s="1">
-        <v>-4.1879884185814682E-2</v>
+        <v>-1.428409148039933E-3</v>
       </c>
       <c r="R24" s="1">
-        <v>-1.5833507538988659E-2</v>
+        <v>-2.4888534492981899E-3</v>
       </c>
       <c r="S24" s="1">
-        <v>-2.2392550138372769E-2</v>
+        <v>6.1539561970100874E-4</v>
       </c>
       <c r="T24" s="1">
-        <v>-6.5454828488855088E-3</v>
+        <v>-1.1224198680324406E-4</v>
       </c>
       <c r="U24" s="1">
-        <v>-1.3793407976392171E-2</v>
+        <v>-5.2619039409512389E-4</v>
       </c>
       <c r="V24" s="1">
-        <v>-4.885596744160331E-2</v>
+        <v>-8.3100201282312186E-4</v>
       </c>
       <c r="W24" s="1">
-        <v>-4.1477886583184909E-2</v>
+        <v>1.2524388977793247E-4</v>
       </c>
       <c r="X24" s="1">
-        <v>3.0431417651178488E-2</v>
+        <v>-1.6407986389393495E-3</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.26471221834155251</v>
+        <v>7.6617251396143699E-3</v>
       </c>
       <c r="Z24" s="1">
-        <v>7.5909495928483062E-2</v>
+        <v>2.5271771226697357E-3</v>
       </c>
       <c r="AA24" s="1">
-        <v>-9.6890812606388182E-2</v>
+        <v>3.5731260683861937E-3</v>
       </c>
       <c r="AB24" s="1">
-        <v>-0.20038939603452061</v>
+        <v>1.5957499991113705E-3</v>
       </c>
       <c r="AC24" s="1">
-        <v>-0.1870490519573717</v>
+        <v>2.7674990050218545E-3</v>
       </c>
       <c r="AD24" s="1">
-        <v>1.216547236039631E-2</v>
+        <v>1.3330495362239951E-3</v>
       </c>
       <c r="AE24" s="1">
-        <v>3.3687831177847183E-2</v>
+        <v>1.7121151955952624E-3</v>
       </c>
       <c r="AF24" s="1">
-        <v>5.527152171926019E-2</v>
+        <v>4.7220737298128007E-4</v>
       </c>
       <c r="AG24" s="1">
-        <v>7.4815878976992697E-2</v>
+        <v>2.0999846682407189E-4</v>
       </c>
       <c r="AH24" s="1">
-        <v>0.12967519543259809</v>
+        <v>6.2775999192364595E-4</v>
       </c>
       <c r="AI24" s="1">
-        <v>5.5953026847501003E-2</v>
+        <v>3.0553301578231384E-3</v>
       </c>
       <c r="AJ24" s="1">
-        <v>-0.13173541022504839</v>
+        <v>-3.6826859106653953E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="1">
-        <v>-0.1651021159635104</v>
+        <v>-0.15945260717039964</v>
       </c>
       <c r="C25" s="1">
-        <v>-1.252334927000795E-2</v>
+        <v>-1.3272246129122471E-3</v>
       </c>
       <c r="D25" s="1">
-        <v>-1.8524624925212629E-2</v>
+        <v>-2.5432650169475782E-3</v>
       </c>
       <c r="E25" s="1">
-        <v>-6.2236956195012294E-3</v>
+        <v>-2.0076494897728475E-3</v>
       </c>
       <c r="F25" s="1">
-        <v>-5.704049888524132E-4</v>
+        <v>-2.1156575669295796E-3</v>
       </c>
       <c r="G25" s="1">
-        <v>-1.9187990188015591E-2</v>
+        <v>-2.476168439548199E-3</v>
       </c>
       <c r="H25" s="1">
-        <v>0.26785783237521571</v>
+        <v>4.0037630269441661E-3</v>
       </c>
       <c r="I25" s="1">
-        <v>4.9831047279614932E-2</v>
+        <v>-4.1642169312211402E-3</v>
       </c>
       <c r="J25" s="1">
-        <v>3.1850737057619018E-2</v>
+        <v>-2.7655703674008061E-3</v>
       </c>
       <c r="K25" s="1">
-        <v>6.4806369493712879E-2</v>
+        <v>1.7343053461902165E-3</v>
       </c>
       <c r="L25" s="1">
-        <v>-1.529246686459825E-2</v>
+        <v>-9.8392025919412482E-4</v>
       </c>
       <c r="M25" s="1">
-        <v>1.9816755006369619E-2</v>
+        <v>6.9204782809432173E-4</v>
       </c>
       <c r="N25" s="1">
-        <v>0.1029910892983512</v>
+        <v>-7.9124273040359627E-4</v>
       </c>
       <c r="O25" s="1">
-        <v>-9.9331667053556894E-2</v>
+        <v>-2.379680060327502E-3</v>
       </c>
       <c r="P25" s="1">
-        <v>-3.044953541226714E-2</v>
+        <v>-2.2874269095505481E-3</v>
       </c>
       <c r="Q25" s="1">
-        <v>-1.035415697810649E-2</v>
+        <v>-1.1452469130368292E-3</v>
       </c>
       <c r="R25" s="1">
-        <v>-4.8724734617202843E-2</v>
+        <v>-1.757459199111279E-3</v>
       </c>
       <c r="S25" s="1">
-        <v>1.184444104930937E-2</v>
+        <v>1.6021121126774396E-3</v>
       </c>
       <c r="T25" s="1">
-        <v>3.3548992081554929E-2</v>
+        <v>5.2651162890981276E-3</v>
       </c>
       <c r="U25" s="1">
-        <v>-2.1612336665595921E-2</v>
+        <v>-1.6501795426561786E-3</v>
       </c>
       <c r="V25" s="1">
-        <v>1.1924855021535291E-2</v>
+        <v>1.0388365469483629E-3</v>
       </c>
       <c r="W25" s="1">
-        <v>-3.308873099386378E-2</v>
+        <v>-2.2596607626433618E-3</v>
       </c>
       <c r="X25" s="1">
-        <v>-5.2536173860719473E-2</v>
+        <v>-2.5787145194650272E-3</v>
       </c>
       <c r="Y25" s="1">
-        <v>7.5909495928483062E-2</v>
+        <v>2.5271771226697357E-3</v>
       </c>
       <c r="Z25" s="1">
-        <v>0.33921253750545088</v>
+        <v>1.1934094154987774E-2</v>
       </c>
       <c r="AA25" s="1">
-        <v>0.16037019970425229</v>
+        <v>9.893780084279772E-3</v>
       </c>
       <c r="AB25" s="1">
-        <v>0.16838649536968689</v>
+        <v>1.1560544771566747E-2</v>
       </c>
       <c r="AC25" s="1">
-        <v>0.18105662467946981</v>
+        <v>8.7979401275479381E-3</v>
       </c>
       <c r="AD25" s="1">
-        <v>-5.1740512987952618E-2</v>
+        <v>1.2380467999549248E-3</v>
       </c>
       <c r="AE25" s="1">
-        <v>1.643812677497088E-2</v>
+        <v>2.1043499287845893E-3</v>
       </c>
       <c r="AF25" s="1">
-        <v>3.8251219876564019E-2</v>
+        <v>3.2822053591937336E-3</v>
       </c>
       <c r="AG25" s="1">
-        <v>4.248508108287502E-2</v>
+        <v>7.4995686459730301E-4</v>
       </c>
       <c r="AH25" s="1">
-        <v>0.1774765001667982</v>
+        <v>4.0355622762079102E-3</v>
       </c>
       <c r="AI25" s="1">
-        <v>7.5268965855211423E-2</v>
+        <v>3.3676235433720489E-3</v>
       </c>
       <c r="AJ25" s="1">
-        <v>-0.15477999190839159</v>
+        <v>9.8322876457008213E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="1">
-        <v>-0.35315728695663812</v>
+        <v>-0.26730681359777086</v>
       </c>
       <c r="C26" s="1">
-        <v>7.8694054560778433E-3</v>
+        <v>-3.2487428993974339E-4</v>
       </c>
       <c r="D26" s="1">
-        <v>7.0725960061235923E-2</v>
+        <v>-2.4077046779181939E-3</v>
       </c>
       <c r="E26" s="1">
-        <v>-3.9545590440357584E-3</v>
+        <v>-2.6698238092818967E-3</v>
       </c>
       <c r="F26" s="1">
-        <v>3.9262907695380232E-2</v>
+        <v>-1.7753436404568147E-3</v>
       </c>
       <c r="G26" s="1">
-        <v>-3.6030908663734901E-3</v>
+        <v>-3.7445090522147412E-3</v>
       </c>
       <c r="H26" s="1">
-        <v>-1.242018660926412E-2</v>
+        <v>2.1390162896154016E-3</v>
       </c>
       <c r="I26" s="1">
-        <v>-6.5063588414725537E-2</v>
+        <v>-4.2638508304366643E-3</v>
       </c>
       <c r="J26" s="1">
-        <v>-0.1118115359924889</v>
+        <v>-2.4975136293723119E-3</v>
       </c>
       <c r="K26" s="1">
-        <v>-5.269424450619839E-2</v>
+        <v>5.1300446736904978E-4</v>
       </c>
       <c r="L26" s="1">
-        <v>1.3246853112916139E-2</v>
+        <v>-1.1734991501480432E-3</v>
       </c>
       <c r="M26" s="1">
-        <v>-3.7498264962674221E-2</v>
+        <v>1.1603592097122132E-3</v>
       </c>
       <c r="N26" s="1">
-        <v>-0.1008746791087496</v>
+        <v>-2.4613944892730444E-4</v>
       </c>
       <c r="O26" s="1">
-        <v>6.0459501818327432E-2</v>
+        <v>-7.5927318620427897E-4</v>
       </c>
       <c r="P26" s="1">
-        <v>-4.1669630245641409E-2</v>
+        <v>-9.8910896790193464E-4</v>
       </c>
       <c r="Q26" s="1">
-        <v>-2.992347081207369E-2</v>
+        <v>2.8978075386659058E-4</v>
       </c>
       <c r="R26" s="1">
-        <v>-4.9843488947988512E-2</v>
+        <v>-4.769868334737512E-3</v>
       </c>
       <c r="S26" s="1">
-        <v>-3.4811615348104397E-2</v>
+        <v>2.2937784364473121E-3</v>
       </c>
       <c r="T26" s="1">
-        <v>-2.0059533657790118E-2</v>
+        <v>8.7175631950267216E-3</v>
       </c>
       <c r="U26" s="1">
-        <v>-4.842290196857546E-2</v>
+        <v>-6.3860514131400259E-4</v>
       </c>
       <c r="V26" s="1">
-        <v>-3.656541171883632E-3</v>
+        <v>3.2126117483656652E-3</v>
       </c>
       <c r="W26" s="1">
-        <v>-3.2064715871190419E-2</v>
+        <v>8.0185380917747323E-4</v>
       </c>
       <c r="X26" s="1">
-        <v>-3.92826521172292E-2</v>
+        <v>-5.485377876734799E-3</v>
       </c>
       <c r="Y26" s="1">
-        <v>-9.6890812606388182E-2</v>
+        <v>3.5731260683861937E-3</v>
       </c>
       <c r="Z26" s="1">
-        <v>0.16037019970425229</v>
+        <v>9.893780084279772E-3</v>
       </c>
       <c r="AA26" s="1">
-        <v>0.24939164295795799</v>
+        <v>1.5321105778784025E-2</v>
       </c>
       <c r="AB26" s="1">
-        <v>0.25581002628441518</v>
+        <v>1.5334792484944751E-2</v>
       </c>
       <c r="AC26" s="1">
-        <v>0.25907224601697287</v>
+        <v>1.1782246502201991E-2</v>
       </c>
       <c r="AD26" s="1">
-        <v>-2.1465105991577031E-2</v>
+        <v>1.0795686089698914E-3</v>
       </c>
       <c r="AE26" s="1">
-        <v>-2.5038179615530752E-3</v>
+        <v>3.7816187374137694E-3</v>
       </c>
       <c r="AF26" s="1">
-        <v>-1.069424871592237E-2</v>
+        <v>4.4878636307167791E-3</v>
       </c>
       <c r="AG26" s="1">
-        <v>-1.8548276293834279E-2</v>
+        <v>8.7615115638158686E-4</v>
       </c>
       <c r="AH26" s="1">
-        <v>-1.6045978067392941E-2</v>
+        <v>3.5819061539435482E-3</v>
       </c>
       <c r="AI26" s="1">
-        <v>4.8558992847194948E-2</v>
+        <v>5.183089894500989E-3</v>
       </c>
       <c r="AJ26" s="1">
-        <v>-0.1377750642963369</v>
+        <v>-4.1063908730908372E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="1">
-        <v>-0.74533153350686654</v>
+        <v>-0.23385275544311643</v>
       </c>
       <c r="C27" s="1">
-        <v>-1.1943973934407491E-2</v>
+        <v>-4.0190504676308747E-3</v>
       </c>
       <c r="D27" s="1">
-        <v>5.7654457747829978E-2</v>
+        <v>-1.602180209109838E-2</v>
       </c>
       <c r="E27" s="1">
-        <v>-6.4734131400476569E-2</v>
+        <v>-1.0023852219392032E-2</v>
       </c>
       <c r="F27" s="1">
-        <v>-9.7211995100152659E-3</v>
+        <v>-8.0469800128721083E-3</v>
       </c>
       <c r="G27" s="1">
-        <v>-4.6152807169387418E-2</v>
+        <v>-9.9476277200388624E-3</v>
       </c>
       <c r="H27" s="1">
-        <v>-1.0717405549841959E-2</v>
+        <v>1.2942522400641043E-2</v>
       </c>
       <c r="I27" s="1">
-        <v>-2.139522957476063E-2</v>
+        <v>-3.9705436718061498E-3</v>
       </c>
       <c r="J27" s="1">
-        <v>-0.20058060799018179</v>
+        <v>1.4525049168606467E-3</v>
       </c>
       <c r="K27" s="1">
-        <v>-0.23449003677657829</v>
+        <v>-1.0468728569991322E-3</v>
       </c>
       <c r="L27" s="1">
-        <v>4.3491314082666127E-2</v>
+        <v>-3.0040032598688247E-3</v>
       </c>
       <c r="M27" s="1">
-        <v>-9.7227761864754791E-2</v>
+        <v>2.6306722155599598E-3</v>
       </c>
       <c r="N27" s="1">
-        <v>-5.4711869501649968E-2</v>
+        <v>-2.9219972655924187E-3</v>
       </c>
       <c r="O27" s="1">
-        <v>0.37279351243385811</v>
+        <v>-6.7727835518016644E-3</v>
       </c>
       <c r="P27" s="1">
-        <v>-5.5634215489188121E-2</v>
+        <v>5.0260311100938648E-4</v>
       </c>
       <c r="Q27" s="1">
-        <v>5.0259021286431449E-2</v>
+        <v>2.5451472577105727E-3</v>
       </c>
       <c r="R27" s="1">
-        <v>-8.9546127448600354E-2</v>
+        <v>-1.0765646352698471E-2</v>
       </c>
       <c r="S27" s="1">
-        <v>7.4099198054716098E-2</v>
+        <v>6.3904170043979358E-3</v>
       </c>
       <c r="T27" s="1">
-        <v>6.4293936426133236E-2</v>
+        <v>2.6810153255624358E-2</v>
       </c>
       <c r="U27" s="1">
-        <v>-5.0116023934231091E-2</v>
+        <v>1.3390219490333477E-3</v>
       </c>
       <c r="V27" s="1">
-        <v>5.9557322080621811E-2</v>
+        <v>3.9763277652014317E-3</v>
       </c>
       <c r="W27" s="1">
-        <v>-1.0140289045093681E-2</v>
+        <v>-3.5942009547263731E-3</v>
       </c>
       <c r="X27" s="1">
-        <v>-0.16301382573154091</v>
+        <v>-1.2413995084986815E-2</v>
       </c>
       <c r="Y27" s="1">
-        <v>-0.20038939603452061</v>
+        <v>1.5957499991113705E-3</v>
       </c>
       <c r="Z27" s="1">
-        <v>0.16838649536968689</v>
+        <v>1.1560544771566747E-2</v>
       </c>
       <c r="AA27" s="1">
-        <v>0.25581002628441518</v>
+        <v>1.5334792484944751E-2</v>
       </c>
       <c r="AB27" s="1">
-        <v>0.52422631882298321</v>
+        <v>2.8130131003335557E-2</v>
       </c>
       <c r="AC27" s="1">
-        <v>0.47356641975440461</v>
+        <v>1.0224722921127711E-2</v>
       </c>
       <c r="AD27" s="1">
-        <v>-3.4393539018309417E-2</v>
+        <v>-4.2255921408193564E-4</v>
       </c>
       <c r="AE27" s="1">
-        <v>-4.5392607891061462E-2</v>
+        <v>3.338219839882816E-3</v>
       </c>
       <c r="AF27" s="1">
-        <v>-3.09405912802364E-2</v>
+        <v>1.5009063997144884E-2</v>
       </c>
       <c r="AG27" s="1">
-        <v>-8.2167039836225586E-2</v>
+        <v>4.4338517458406071E-3</v>
       </c>
       <c r="AH27" s="1">
-        <v>-1.049850168634275E-2</v>
+        <v>1.1742721463925639E-2</v>
       </c>
       <c r="AI27" s="1">
-        <v>-3.6698822282365822E-3</v>
+        <v>6.7485286334156118E-3</v>
       </c>
       <c r="AJ27" s="1">
-        <v>0.176727313993676</v>
+        <v>4.2475290648051778E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B28" s="1">
-        <v>-0.74801036478283889</v>
+        <v>-0.38190757202461573</v>
       </c>
       <c r="C28" s="1">
-        <v>-9.6373386044443041E-3</v>
+        <v>3.2636442211320576E-3</v>
       </c>
       <c r="D28" s="1">
-        <v>0.1033298474288723</v>
+        <v>9.8600112319026916E-3</v>
       </c>
       <c r="E28" s="1">
-        <v>-6.6158829101653549E-2</v>
+        <v>-2.210950445406621E-4</v>
       </c>
       <c r="F28" s="1">
-        <v>-1.8830615865961099E-3</v>
+        <v>2.2336091618963229E-3</v>
       </c>
       <c r="G28" s="1">
-        <v>-3.3928416110938497E-2</v>
+        <v>1.0497823307237635E-3</v>
       </c>
       <c r="H28" s="1">
-        <v>1.118122798890599E-2</v>
+        <v>-3.8530879102744386E-3</v>
       </c>
       <c r="I28" s="1">
-        <v>-2.3022200714247279E-2</v>
+        <v>-5.4888772603512419E-3</v>
       </c>
       <c r="J28" s="1">
-        <v>-0.2480509686799173</v>
+        <v>-9.7300677501514221E-3</v>
       </c>
       <c r="K28" s="1">
-        <v>-0.1908476820643413</v>
+        <v>-2.2142878856084474E-4</v>
       </c>
       <c r="L28" s="1">
-        <v>5.2457582755240317E-2</v>
+        <v>1.3267683324525278E-3</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.1282237095936157</v>
+        <v>-1.5382695424149425E-3</v>
       </c>
       <c r="N28" s="1">
-        <v>-2.129651796574528E-2</v>
+        <v>9.4021732705720784E-4</v>
       </c>
       <c r="O28" s="1">
-        <v>0.35674610927256772</v>
+        <v>2.2903818695744135E-3</v>
       </c>
       <c r="P28" s="1">
-        <v>-5.5111813428252332E-2</v>
+        <v>-4.9439397674655178E-3</v>
       </c>
       <c r="Q28" s="1">
-        <v>5.811587804936369E-2</v>
+        <v>-2.3989351535690165E-3</v>
       </c>
       <c r="R28" s="1">
-        <v>-2.1555417308550599E-2</v>
+        <v>-3.6760917863221179E-3</v>
       </c>
       <c r="S28" s="1">
-        <v>8.3136241024189483E-2</v>
+        <v>2.6391449387385552E-5</v>
       </c>
       <c r="T28" s="1">
-        <v>6.1811022205548238E-2</v>
+        <v>-4.1870805565211583E-3</v>
       </c>
       <c r="U28" s="1">
-        <v>-1.841064179989849E-2</v>
+        <v>-6.6076880129388033E-3</v>
       </c>
       <c r="V28" s="1">
-        <v>7.1381626679946075E-2</v>
+        <v>5.3791021107371662E-4</v>
       </c>
       <c r="W28" s="1">
-        <v>1.0247861719041461E-2</v>
+        <v>1.1092501836849067E-3</v>
       </c>
       <c r="X28" s="1">
-        <v>-0.15790694804321409</v>
+        <v>-2.0436933254905153E-3</v>
       </c>
       <c r="Y28" s="1">
-        <v>-0.1870490519573717</v>
+        <v>2.7674990050218545E-3</v>
       </c>
       <c r="Z28" s="1">
-        <v>0.18105662467946981</v>
+        <v>8.7979401275479381E-3</v>
       </c>
       <c r="AA28" s="1">
-        <v>0.25907224601697287</v>
+        <v>1.1782246502201991E-2</v>
       </c>
       <c r="AB28" s="1">
-        <v>0.47356641975440461</v>
+        <v>1.0224722921127711E-2</v>
       </c>
       <c r="AC28" s="1">
-        <v>0.54406901649698725</v>
+        <v>2.2555664298875344E-2</v>
       </c>
       <c r="AD28" s="1">
-        <v>1.9450821635713971E-2</v>
+        <v>5.5401170983899219E-3</v>
       </c>
       <c r="AE28" s="1">
-        <v>8.3448079689859914E-3</v>
+        <v>2.8626058707116771E-3</v>
       </c>
       <c r="AF28" s="1">
-        <v>1.772241429649515E-2</v>
+        <v>6.6718894716942534E-4</v>
       </c>
       <c r="AG28" s="1">
-        <v>-3.3644162487650307E-2</v>
+        <v>-1.4087303371374781E-3</v>
       </c>
       <c r="AH28" s="1">
-        <v>2.463830131803663E-2</v>
+        <v>-3.4673659557474465E-3</v>
       </c>
       <c r="AI28" s="1">
-        <v>3.7958050808642577E-2</v>
+        <v>3.4109421720668991E-3</v>
       </c>
       <c r="AJ28" s="1">
-        <v>6.2611639792251594E-2</v>
+        <v>-4.5626095317895077E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B29" s="1">
-        <v>-0.3599747509330789</v>
+        <v>-6.4618994064124052E-2</v>
       </c>
       <c r="C29" s="1">
-        <v>5.7234287031351482E-4</v>
+        <v>6.6147154844984485E-4</v>
       </c>
       <c r="D29" s="1">
-        <v>8.2477350755392309E-2</v>
+        <v>5.6670533432064893E-3</v>
       </c>
       <c r="E29" s="1">
-        <v>1.1811030142779501E-3</v>
+        <v>-3.0375730982877547E-3</v>
       </c>
       <c r="F29" s="1">
-        <v>6.7320189375223256E-3</v>
+        <v>-1.5572300905417544E-3</v>
       </c>
       <c r="G29" s="1">
-        <v>1.5272554657526371E-2</v>
+        <v>-4.6693465537058637E-4</v>
       </c>
       <c r="H29" s="1">
-        <v>-5.304762958926415E-3</v>
+        <v>1.3830130378222668E-3</v>
       </c>
       <c r="I29" s="1">
-        <v>-2.5262136109211481E-2</v>
+        <v>-6.8301940960749288E-4</v>
       </c>
       <c r="J29" s="1">
-        <v>-7.7918470840034518E-2</v>
+        <v>3.6247816681104356E-5</v>
       </c>
       <c r="K29" s="1">
-        <v>6.3849623130647001E-3</v>
+        <v>2.9229449617708785E-3</v>
       </c>
       <c r="L29" s="1">
-        <v>2.175852007084406E-2</v>
+        <v>1.0991657235865098E-4</v>
       </c>
       <c r="M29" s="1">
-        <v>-8.4871065069188081E-2</v>
+        <v>-1.4156494645343209E-3</v>
       </c>
       <c r="N29" s="1">
-        <v>-2.892373048335262E-2</v>
+        <v>3.6878157404607315E-5</v>
       </c>
       <c r="O29" s="1">
-        <v>0.1193842375277476</v>
+        <v>-6.6418699222811628E-4</v>
       </c>
       <c r="P29" s="1">
-        <v>-1.706882875372304E-2</v>
+        <v>-2.2540898047195418E-3</v>
       </c>
       <c r="Q29" s="1">
-        <v>1.9685005994262789E-2</v>
+        <v>-1.0586511528963699E-3</v>
       </c>
       <c r="R29" s="1">
-        <v>7.6230643299781603E-2</v>
+        <v>1.9406939282684971E-3</v>
       </c>
       <c r="S29" s="1">
-        <v>3.6079963637511037E-2</v>
+        <v>6.6870376208620214E-3</v>
       </c>
       <c r="T29" s="1">
-        <v>3.941263185194166E-2</v>
+        <v>1.8700051501530229E-3</v>
       </c>
       <c r="U29" s="1">
-        <v>8.6186766584949448E-3</v>
+        <v>-2.9942960228746401E-3</v>
       </c>
       <c r="V29" s="1">
-        <v>1.446823903934533E-2</v>
+        <v>-2.6480092218950091E-5</v>
       </c>
       <c r="W29" s="1">
-        <v>-1.363409448500136E-3</v>
+        <v>-6.5330046727028745E-4</v>
       </c>
       <c r="X29" s="1">
-        <v>-1.6876516050397871E-2</v>
+        <v>7.8346174502820585E-4</v>
       </c>
       <c r="Y29" s="1">
-        <v>1.216547236039631E-2</v>
+        <v>1.3330495362239951E-3</v>
       </c>
       <c r="Z29" s="1">
-        <v>-5.1740512987952618E-2</v>
+        <v>1.2380467999549248E-3</v>
       </c>
       <c r="AA29" s="1">
-        <v>-2.1465105991577031E-2</v>
+        <v>1.0795686089698914E-3</v>
       </c>
       <c r="AB29" s="1">
-        <v>-3.4393539018309417E-2</v>
+        <v>-4.2255921408193564E-4</v>
       </c>
       <c r="AC29" s="1">
-        <v>1.9450821635713971E-2</v>
+        <v>5.5401170983899219E-3</v>
       </c>
       <c r="AD29" s="1">
-        <v>0.2235706487669793</v>
+        <v>1.5338976623308791E-2</v>
       </c>
       <c r="AE29" s="1">
-        <v>0.12403287136426309</v>
+        <v>4.8800251557789068E-3</v>
       </c>
       <c r="AF29" s="1">
-        <v>0.1329173783606494</v>
+        <v>8.3733825260408901E-3</v>
       </c>
       <c r="AG29" s="1">
-        <v>0.1197489615605271</v>
+        <v>5.0473833827225645E-3</v>
       </c>
       <c r="AH29" s="1">
-        <v>0.1053377608157343</v>
+        <v>2.5253752172187394E-3</v>
       </c>
       <c r="AI29" s="1">
-        <v>0.1333474809182458</v>
+        <v>7.3865029021230114E-3</v>
       </c>
       <c r="AJ29" s="1">
-        <v>-0.1059329189807081</v>
+        <v>-1.7486716778097766E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B30" s="1">
-        <v>-0.23077639772677391</v>
+        <v>-7.5612475776232618E-2</v>
       </c>
       <c r="C30" s="1">
-        <v>2.630341538207721E-3</v>
+        <v>-2.4600156275379932E-3</v>
       </c>
       <c r="D30" s="1">
-        <v>1.2180525606093281E-2</v>
+        <v>-5.3027277909500695E-3</v>
       </c>
       <c r="E30" s="1">
-        <v>6.3090251288320728E-4</v>
+        <v>1.9874833144937834E-3</v>
       </c>
       <c r="F30" s="1">
-        <v>1.142164444114295E-2</v>
+        <v>-2.3519820810124735E-3</v>
       </c>
       <c r="G30" s="1">
-        <v>-2.011618104891064E-2</v>
+        <v>-2.2856855549261111E-3</v>
       </c>
       <c r="H30" s="1">
-        <v>4.4543546768585629E-2</v>
+        <v>-1.3338804467912871E-3</v>
       </c>
       <c r="I30" s="1">
-        <v>1.2397934509719049E-2</v>
+        <v>-1.3689405567373428E-3</v>
       </c>
       <c r="J30" s="1">
-        <v>1.285159387322374E-2</v>
+        <v>1.655937197115603E-3</v>
       </c>
       <c r="K30" s="1">
-        <v>1.454267234609833E-2</v>
+        <v>4.8530740309433301E-4</v>
       </c>
       <c r="L30" s="1">
-        <v>9.9869155051263737E-3</v>
+        <v>-1.7009964982481326E-3</v>
       </c>
       <c r="M30" s="1">
-        <v>-2.5143171476109019E-2</v>
+        <v>-7.0484902597614833E-4</v>
       </c>
       <c r="N30" s="1">
-        <v>-5.2427909555444498E-2</v>
+        <v>-1.0654819231160906E-3</v>
       </c>
       <c r="O30" s="1">
-        <v>-6.4528370723981807E-2</v>
+        <v>-1.2801243109899774E-3</v>
       </c>
       <c r="P30" s="1">
-        <v>-5.5776238593592382E-2</v>
+        <v>-2.0912026714829113E-3</v>
       </c>
       <c r="Q30" s="1">
-        <v>-4.1541439231067873E-2</v>
+        <v>-2.0495463820457555E-3</v>
       </c>
       <c r="R30" s="1">
-        <v>-5.2160538451774957E-3</v>
+        <v>7.990413178978889E-4</v>
       </c>
       <c r="S30" s="1">
-        <v>-2.8538916703326062E-2</v>
+        <v>3.0214763491670515E-3</v>
       </c>
       <c r="T30" s="1">
-        <v>1.213817839381892E-2</v>
+        <v>1.0666465039247591E-2</v>
       </c>
       <c r="U30" s="1">
-        <v>-2.0782954332979071E-2</v>
+        <v>2.980144449170552E-3</v>
       </c>
       <c r="V30" s="1">
-        <v>-2.082377716608351E-2</v>
+        <v>1.9288124436450671E-3</v>
       </c>
       <c r="W30" s="1">
-        <v>-3.3446217676563791E-2</v>
+        <v>-4.8705202788484891E-4</v>
       </c>
       <c r="X30" s="1">
-        <v>-1.0062031867711631E-2</v>
+        <v>-1.1181121633983097E-3</v>
       </c>
       <c r="Y30" s="1">
-        <v>3.3687831177847183E-2</v>
+        <v>1.7121151955952624E-3</v>
       </c>
       <c r="Z30" s="1">
-        <v>1.643812677497088E-2</v>
+        <v>2.1043499287845893E-3</v>
       </c>
       <c r="AA30" s="1">
-        <v>-2.5038179615530752E-3</v>
+        <v>3.7816187374137694E-3</v>
       </c>
       <c r="AB30" s="1">
-        <v>-4.5392607891061462E-2</v>
+        <v>3.338219839882816E-3</v>
       </c>
       <c r="AC30" s="1">
-        <v>8.3448079689859914E-3</v>
+        <v>2.8626058707116771E-3</v>
       </c>
       <c r="AD30" s="1">
-        <v>0.12403287136426309</v>
+        <v>4.8800251557789068E-3</v>
       </c>
       <c r="AE30" s="1">
-        <v>0.18073443521871929</v>
+        <v>1.6497041610589867E-2</v>
       </c>
       <c r="AF30" s="1">
-        <v>0.1260771273954451</v>
+        <v>5.98345593120507E-3</v>
       </c>
       <c r="AG30" s="1">
-        <v>0.13415210168174321</v>
+        <v>6.1316509084079502E-3</v>
       </c>
       <c r="AH30" s="1">
-        <v>0.14289653748098929</v>
+        <v>8.1972892774560546E-3</v>
       </c>
       <c r="AI30" s="1">
-        <v>0.1599543691564998</v>
+        <v>6.8871704353699152E-3</v>
       </c>
       <c r="AJ30" s="1">
-        <v>-0.14574799931140611</v>
+        <v>2.2226365118538149E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="1">
-        <v>-0.46165922546140142</v>
+        <v>-0.24685806429031357</v>
       </c>
       <c r="C31" s="1">
-        <v>-2.1707381376473321E-3</v>
+        <v>-7.2490859582044487E-4</v>
       </c>
       <c r="D31" s="1">
-        <v>3.3917411151228358E-2</v>
+        <v>-9.3289653234714387E-3</v>
       </c>
       <c r="E31" s="1">
-        <v>-2.687366437567219E-2</v>
+        <v>-1.3991745868894637E-2</v>
       </c>
       <c r="F31" s="1">
-        <v>-1.884594997786692E-2</v>
+        <v>-9.3942656880476802E-3</v>
       </c>
       <c r="G31" s="1">
-        <v>-2.2441024026501791E-2</v>
+        <v>-1.0543017554580737E-2</v>
       </c>
       <c r="H31" s="1">
-        <v>8.7270134001979111E-2</v>
+        <v>2.2017522976082973E-2</v>
       </c>
       <c r="I31" s="1">
-        <v>1.878261717032496E-2</v>
+        <v>2.3691409902991036E-3</v>
       </c>
       <c r="J31" s="1">
-        <v>8.5724139223055974E-3</v>
+        <v>1.1979485823516885E-2</v>
       </c>
       <c r="K31" s="1">
-        <v>3.3009897732817567E-2</v>
+        <v>1.1213940559482577E-4</v>
       </c>
       <c r="L31" s="1">
-        <v>1.3658301156641781E-2</v>
+        <v>-1.9261139630739267E-3</v>
       </c>
       <c r="M31" s="1">
-        <v>-2.8835533963118921E-2</v>
+        <v>2.9204928497593226E-3</v>
       </c>
       <c r="N31" s="1">
-        <v>-2.9478094841397049E-2</v>
+        <v>-4.7045644829181721E-3</v>
       </c>
       <c r="O31" s="1">
-        <v>-6.4807828858669869E-2</v>
+        <v>-7.8903458976185836E-3</v>
       </c>
       <c r="P31" s="1">
-        <v>-2.4539733964498382E-2</v>
+        <v>4.1098700362282026E-3</v>
       </c>
       <c r="Q31" s="1">
-        <v>-4.1400374831276343E-3</v>
+        <v>5.1140522823853451E-3</v>
       </c>
       <c r="R31" s="1">
-        <v>2.4579123244901639E-3</v>
+        <v>-7.4742924887103712E-3</v>
       </c>
       <c r="S31" s="1">
-        <v>1.077262834543458E-3</v>
+        <v>8.9942347059195904E-3</v>
       </c>
       <c r="T31" s="1">
-        <v>4.7516311303259451E-2</v>
+        <v>3.6892363091133085E-2</v>
       </c>
       <c r="U31" s="1">
-        <v>-1.109825607513182E-2</v>
+        <v>-4.3927491333788093E-3</v>
       </c>
       <c r="V31" s="1">
-        <v>-2.416969939227176E-2</v>
+        <v>2.1061930469779E-3</v>
       </c>
       <c r="W31" s="1">
-        <v>-4.2141315406689639E-3</v>
+        <v>4.1448575929914355E-5</v>
       </c>
       <c r="X31" s="1">
-        <v>-3.5785121981088297E-2</v>
+        <v>-1.1061729321517964E-2</v>
       </c>
       <c r="Y31" s="1">
-        <v>5.527152171926019E-2</v>
+        <v>4.7220737298128007E-4</v>
       </c>
       <c r="Z31" s="1">
-        <v>3.8251219876564019E-2</v>
+        <v>3.2822053591937336E-3</v>
       </c>
       <c r="AA31" s="1">
-        <v>-1.069424871592237E-2</v>
+        <v>4.4878636307167791E-3</v>
       </c>
       <c r="AB31" s="1">
-        <v>-3.09405912802364E-2</v>
+        <v>1.5009063997144884E-2</v>
       </c>
       <c r="AC31" s="1">
-        <v>1.772241429649515E-2</v>
+        <v>6.6718894716942534E-4</v>
       </c>
       <c r="AD31" s="1">
-        <v>0.1329173783606494</v>
+        <v>8.3733825260408901E-3</v>
       </c>
       <c r="AE31" s="1">
-        <v>0.1260771273954451</v>
+        <v>5.98345593120507E-3</v>
       </c>
       <c r="AF31" s="1">
-        <v>0.1952917454350365</v>
+        <v>3.2632409691847497E-2</v>
       </c>
       <c r="AG31" s="1">
-        <v>0.16332191202383389</v>
+        <v>9.5387608220213055E-3</v>
       </c>
       <c r="AH31" s="1">
-        <v>0.16580656159026</v>
+        <v>1.1608439750785043E-2</v>
       </c>
       <c r="AI31" s="1">
-        <v>0.17879947484014341</v>
+        <v>1.5214602185497597E-2</v>
       </c>
       <c r="AJ31" s="1">
-        <v>-0.13435550836996879</v>
+        <v>-4.234654867208032E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B32" s="1">
-        <v>4.102013012888512E-2</v>
+        <v>3.7433306955354677E-2</v>
       </c>
       <c r="C32" s="1">
-        <v>-1.4269800098927841E-3</v>
+        <v>-3.2378118976767699E-3</v>
       </c>
       <c r="D32" s="1">
-        <v>2.204091527341745E-2</v>
+        <v>-7.6647083324743667E-3</v>
       </c>
       <c r="E32" s="1">
-        <v>-6.2375510128035777E-3</v>
+        <v>-2.1961956801939964E-3</v>
       </c>
       <c r="F32" s="1">
-        <v>-1.633818124965598E-2</v>
+        <v>-4.0771470002891504E-3</v>
       </c>
       <c r="G32" s="1">
-        <v>-2.3445445531073611E-2</v>
+        <v>-3.3953999051058066E-3</v>
       </c>
       <c r="H32" s="1">
-        <v>9.1839826104090097E-2</v>
+        <v>4.4064724059021867E-3</v>
       </c>
       <c r="I32" s="1">
-        <v>-4.0499252458409043E-3</v>
+        <v>-2.1730539023692621E-4</v>
       </c>
       <c r="J32" s="1">
-        <v>2.788724146944959E-2</v>
+        <v>2.8404846035171554E-3</v>
       </c>
       <c r="K32" s="1">
-        <v>6.784544712185557E-2</v>
+        <v>1.3276764001764916E-3</v>
       </c>
       <c r="L32" s="1">
-        <v>1.234576429497752E-2</v>
+        <v>-1.7975829881613577E-3</v>
       </c>
       <c r="M32" s="1">
-        <v>6.1764362147172054E-3</v>
+        <v>-1.8448808312911081E-4</v>
       </c>
       <c r="N32" s="1">
-        <v>-1.4187386860828041E-2</v>
+        <v>-8.7603846681556796E-4</v>
       </c>
       <c r="O32" s="1">
-        <v>-0.16950526014813791</v>
+        <v>-3.4627533623649148E-3</v>
       </c>
       <c r="P32" s="1">
-        <v>-1.4471948753321541E-2</v>
+        <v>9.7712573496037958E-4</v>
       </c>
       <c r="Q32" s="1">
-        <v>-9.366277230762235E-3</v>
+        <v>6.9971095446783038E-4</v>
       </c>
       <c r="R32" s="1">
-        <v>-3.7762945080939409E-4</v>
+        <v>-1.2558074642224915E-3</v>
       </c>
       <c r="S32" s="1">
-        <v>-1.080602226668788E-2</v>
+        <v>5.8284387990000658E-3</v>
       </c>
       <c r="T32" s="1">
-        <v>1.6219710160822871E-2</v>
+        <v>1.2250506059719293E-2</v>
       </c>
       <c r="U32" s="1">
-        <v>-4.31472458447206E-3</v>
+        <v>3.8842723260856388E-3</v>
       </c>
       <c r="V32" s="1">
-        <v>-3.5660326873474812E-2</v>
+        <v>2.0115787061199264E-4</v>
       </c>
       <c r="W32" s="1">
-        <v>3.0816319005545781E-2</v>
+        <v>-1.7354099892290392E-3</v>
       </c>
       <c r="X32" s="1">
-        <v>-1.2578098641603931E-2</v>
+        <v>-3.2671275593396491E-3</v>
       </c>
       <c r="Y32" s="1">
-        <v>7.4815878976992697E-2</v>
+        <v>2.0999846682407189E-4</v>
       </c>
       <c r="Z32" s="1">
-        <v>4.248508108287502E-2</v>
+        <v>7.4995686459730301E-4</v>
       </c>
       <c r="AA32" s="1">
-        <v>-1.8548276293834279E-2</v>
+        <v>8.7615115638158686E-4</v>
       </c>
       <c r="AB32" s="1">
-        <v>-8.2167039836225586E-2</v>
+        <v>4.4338517458406071E-3</v>
       </c>
       <c r="AC32" s="1">
-        <v>-3.3644162487650307E-2</v>
+        <v>-1.4087303371374781E-3</v>
       </c>
       <c r="AD32" s="1">
-        <v>0.1197489615605271</v>
+        <v>5.0473833827225645E-3</v>
       </c>
       <c r="AE32" s="1">
-        <v>0.13415210168174321</v>
+        <v>6.1316509084079502E-3</v>
       </c>
       <c r="AF32" s="1">
-        <v>0.16332191202383389</v>
+        <v>9.5387608220213055E-3</v>
       </c>
       <c r="AG32" s="1">
-        <v>0.24048538755031559</v>
+        <v>8.8395499400958175E-3</v>
       </c>
       <c r="AH32" s="1">
-        <v>0.17800515679745951</v>
+        <v>9.3600920961429204E-3</v>
       </c>
       <c r="AI32" s="1">
-        <v>0.19459093761390109</v>
+        <v>6.3070951719688979E-3</v>
       </c>
       <c r="AJ32" s="1">
-        <v>-0.16249423835184221</v>
+        <v>3.3821209334910118E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B33" s="1">
-        <v>-1.0337087943975349</v>
+        <v>4.4332315713984161E-2</v>
       </c>
       <c r="C33" s="1">
-        <v>-2.804134274254173E-2</v>
+        <v>-8.1878829083210092E-3</v>
       </c>
       <c r="D33" s="1">
-        <v>-7.8460980729351981E-2</v>
+        <v>-1.970254743761532E-2</v>
       </c>
       <c r="E33" s="1">
-        <v>-7.8239965792529842E-2</v>
+        <v>-3.2923600037883943E-3</v>
       </c>
       <c r="F33" s="1">
-        <v>-7.3588804005110114E-2</v>
+        <v>-8.5575703986695839E-3</v>
       </c>
       <c r="G33" s="1">
-        <v>-6.2425361310386063E-2</v>
+        <v>-6.2707635465372447E-3</v>
       </c>
       <c r="H33" s="1">
-        <v>0.30691261617536902</v>
+        <v>9.3500937180103494E-3</v>
       </c>
       <c r="I33" s="1">
-        <v>0.16085057345829731</v>
+        <v>-1.3784614811090841E-3</v>
       </c>
       <c r="J33" s="1">
-        <v>0.11399840033742439</v>
+        <v>3.9803030710750358E-3</v>
       </c>
       <c r="K33" s="1">
-        <v>5.07046208863558E-2</v>
+        <v>1.9492514316756249E-3</v>
       </c>
       <c r="L33" s="1">
-        <v>1.0493768750307381E-3</v>
+        <v>-3.9180553932853836E-3</v>
       </c>
       <c r="M33" s="1">
-        <v>-2.9015787690659711E-2</v>
+        <v>3.5340619446813095E-4</v>
       </c>
       <c r="N33" s="1">
-        <v>0.25914974124115853</v>
+        <v>-7.7735987361274295E-4</v>
       </c>
       <c r="O33" s="1">
-        <v>4.7546023568520328E-2</v>
+        <v>-5.9236506907795194E-3</v>
       </c>
       <c r="P33" s="1">
-        <v>9.3991909255082273E-2</v>
+        <v>2.8464773306402236E-3</v>
       </c>
       <c r="Q33" s="1">
-        <v>0.11995639215339329</v>
+        <v>1.2409581083864252E-3</v>
       </c>
       <c r="R33" s="1">
-        <v>1.9536546999857188E-2</v>
+        <v>-1.666189969652121E-3</v>
       </c>
       <c r="S33" s="1">
-        <v>0.1651219428376316</v>
+        <v>9.6649586839266111E-3</v>
       </c>
       <c r="T33" s="1">
-        <v>0.19565988774065349</v>
+        <v>2.2832208666158621E-2</v>
       </c>
       <c r="U33" s="1">
-        <v>0.1165875439190565</v>
+        <v>1.0586177058758472E-2</v>
       </c>
       <c r="V33" s="1">
-        <v>0.1293093951997015</v>
+        <v>4.0878655532931019E-3</v>
       </c>
       <c r="W33" s="1">
-        <v>5.6656058473455007E-2</v>
+        <v>-3.7619694717319629E-3</v>
       </c>
       <c r="X33" s="1">
-        <v>-0.10518534027886681</v>
+        <v>-6.2469103479201871E-3</v>
       </c>
       <c r="Y33" s="1">
-        <v>0.12967519543259809</v>
+        <v>6.2775999192364595E-4</v>
       </c>
       <c r="Z33" s="1">
-        <v>0.1774765001667982</v>
+        <v>4.0355622762079102E-3</v>
       </c>
       <c r="AA33" s="1">
-        <v>-1.6045978067392941E-2</v>
+        <v>3.5819061539435482E-3</v>
       </c>
       <c r="AB33" s="1">
-        <v>-1.049850168634275E-2</v>
+        <v>1.1742721463925639E-2</v>
       </c>
       <c r="AC33" s="1">
-        <v>2.463830131803663E-2</v>
+        <v>-3.4673659557474465E-3</v>
       </c>
       <c r="AD33" s="1">
-        <v>0.1053377608157343</v>
+        <v>2.5253752172187394E-3</v>
       </c>
       <c r="AE33" s="1">
-        <v>0.14289653748098929</v>
+        <v>8.1972892774560546E-3</v>
       </c>
       <c r="AF33" s="1">
-        <v>0.16580656159026</v>
+        <v>1.1608439750785043E-2</v>
       </c>
       <c r="AG33" s="1">
-        <v>0.17800515679745951</v>
+        <v>9.3600920961429204E-3</v>
       </c>
       <c r="AH33" s="1">
-        <v>0.39519669016382941</v>
+        <v>1.958468379861095E-2</v>
       </c>
       <c r="AI33" s="1">
-        <v>0.17032639445406789</v>
+        <v>6.1173590894425464E-3</v>
       </c>
       <c r="AJ33" s="1">
-        <v>-9.5143503848782895E-2</v>
+        <v>9.2650885080954509E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B34" s="1">
-        <v>-0.31595694373652822</v>
+        <v>-0.16474260733705351</v>
       </c>
       <c r="C34" s="1">
-        <v>1.1886379774604111E-2</v>
+        <v>8.3455379649403569E-4</v>
       </c>
       <c r="D34" s="1">
-        <v>4.695862102039821E-2</v>
+        <v>-3.7458700000946032E-4</v>
       </c>
       <c r="E34" s="1">
-        <v>1.7825835350572829E-2</v>
+        <v>-4.3321291425609532E-3</v>
       </c>
       <c r="F34" s="1">
-        <v>4.5252436564171827E-3</v>
+        <v>-3.5748370279422917E-3</v>
       </c>
       <c r="G34" s="1">
-        <v>-7.0724203009400022E-2</v>
+        <v>-5.9208402991956233E-3</v>
       </c>
       <c r="H34" s="1">
-        <v>5.3794750806988999E-2</v>
+        <v>7.3315294708128052E-3</v>
       </c>
       <c r="I34" s="1">
-        <v>1.5224795864045499E-3</v>
+        <v>2.0485760374980332E-3</v>
       </c>
       <c r="J34" s="1">
-        <v>4.555833388385238E-2</v>
+        <v>7.3563671624393527E-3</v>
       </c>
       <c r="K34" s="1">
-        <v>1.9056127654588459E-2</v>
+        <v>-2.7857104302929283E-4</v>
       </c>
       <c r="L34" s="1">
-        <v>1.8813261701022072E-2</v>
+        <v>-8.8888660592080482E-4</v>
       </c>
       <c r="M34" s="1">
-        <v>-4.4642552350116251E-2</v>
+        <v>4.2366926769203716E-4</v>
       </c>
       <c r="N34" s="1">
-        <v>-0.34362285935060161</v>
+        <v>-4.6855802936645874E-3</v>
       </c>
       <c r="O34" s="1">
-        <v>-0.37916023551692662</v>
+        <v>-5.530614335888806E-3</v>
       </c>
       <c r="P34" s="1">
-        <v>-0.2607523530408532</v>
+        <v>-2.5736466813133796E-4</v>
       </c>
       <c r="Q34" s="1">
-        <v>-0.25718415642123221</v>
+        <v>1.1701821712986615E-4</v>
       </c>
       <c r="R34" s="1">
-        <v>-0.2249613221918714</v>
+        <v>-4.6420098298437379E-3</v>
       </c>
       <c r="S34" s="1">
-        <v>-0.24478508177323541</v>
+        <v>2.3437479256150917E-3</v>
       </c>
       <c r="T34" s="1">
-        <v>-0.21371418308924239</v>
+        <v>1.4555499644513289E-2</v>
       </c>
       <c r="U34" s="1">
-        <v>-0.2531950933020829</v>
+        <v>-5.3780525967735554E-3</v>
       </c>
       <c r="V34" s="1">
-        <v>-0.2608682137584154</v>
+        <v>-5.3310191419034259E-5</v>
       </c>
       <c r="W34" s="1">
-        <v>-0.22685083804772591</v>
+        <v>-3.0050642498025137E-4</v>
       </c>
       <c r="X34" s="1">
-        <v>-3.4747191143682153E-2</v>
+        <v>-4.734312758234392E-3</v>
       </c>
       <c r="Y34" s="1">
-        <v>5.5953026847501003E-2</v>
+        <v>3.0553301578231384E-3</v>
       </c>
       <c r="Z34" s="1">
-        <v>7.5268965855211423E-2</v>
+        <v>3.3676235433720489E-3</v>
       </c>
       <c r="AA34" s="1">
-        <v>4.8558992847194948E-2</v>
+        <v>5.183089894500989E-3</v>
       </c>
       <c r="AB34" s="1">
-        <v>-3.6698822282365822E-3</v>
+        <v>6.7485286334156118E-3</v>
       </c>
       <c r="AC34" s="1">
-        <v>3.7958050808642577E-2</v>
+        <v>3.4109421720668991E-3</v>
       </c>
       <c r="AD34" s="1">
-        <v>0.1333474809182458</v>
+        <v>7.3865029021230114E-3</v>
       </c>
       <c r="AE34" s="1">
-        <v>0.1599543691564998</v>
+        <v>6.8871704353699152E-3</v>
       </c>
       <c r="AF34" s="1">
-        <v>0.17879947484014341</v>
+        <v>1.5214602185497597E-2</v>
       </c>
       <c r="AG34" s="1">
-        <v>0.19459093761390109</v>
+        <v>6.3070951719688979E-3</v>
       </c>
       <c r="AH34" s="1">
-        <v>0.17032639445406789</v>
+        <v>6.1173590894425464E-3</v>
       </c>
       <c r="AI34" s="1">
-        <v>0.37572271349896258</v>
+        <v>1.702675858674934E-2</v>
       </c>
       <c r="AJ34" s="1">
-        <v>-0.11343035991063991</v>
+        <v>-2.0717887566060078E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="1">
-        <v>9.653528694168358</v>
+        <v>3.2855185192134257</v>
       </c>
       <c r="C35" s="1">
-        <v>-7.8270857718464107E-2</v>
+        <v>-8.212449795671567E-2</v>
       </c>
       <c r="D35" s="1">
-        <v>-0.23530672207505671</v>
+        <v>-0.15456548195816794</v>
       </c>
       <c r="E35" s="1">
-        <v>-0.1815310864983295</v>
+        <v>-1.2617962192107535E-2</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.22180643242903469</v>
+        <v>-6.2583426973410072E-2</v>
       </c>
       <c r="G35" s="1">
-        <v>-0.1763764910748834</v>
+        <v>-3.0713017143013888E-2</v>
       </c>
       <c r="H35" s="1">
-        <v>-0.19315396597978249</v>
+        <v>1.606346913141482E-2</v>
       </c>
       <c r="I35" s="1">
-        <v>3.2955208613743243E-2</v>
+        <v>-2.1325097215286255E-2</v>
       </c>
       <c r="J35" s="1">
-        <v>-4.225591869591816E-2</v>
+        <v>-4.1117510520252698E-4</v>
       </c>
       <c r="K35" s="1">
-        <v>-0.27386182137797821</v>
+        <v>1.4738992711229054E-2</v>
       </c>
       <c r="L35" s="1">
-        <v>2.5991790782175551E-2</v>
+        <v>-2.7625918728394261E-2</v>
       </c>
       <c r="M35" s="1">
-        <v>-1.811092278712478E-2</v>
+        <v>-4.8523576626732616E-3</v>
       </c>
       <c r="N35" s="1">
-        <v>-0.70663520596480733</v>
+        <v>-2.1428645288377179E-3</v>
       </c>
       <c r="O35" s="1">
-        <v>-0.53565584672363453</v>
+        <v>-2.8856675272554977E-2</v>
       </c>
       <c r="P35" s="1">
-        <v>-0.79372699276152847</v>
+        <v>9.7026547643392913E-3</v>
       </c>
       <c r="Q35" s="1">
-        <v>-0.7100526280516215</v>
+        <v>4.5009194893514959E-3</v>
       </c>
       <c r="R35" s="1">
-        <v>-0.92194857491685855</v>
+        <v>1.4651890529129963E-2</v>
       </c>
       <c r="S35" s="1">
-        <v>-0.63415478324407992</v>
+        <v>9.049940028705461E-2</v>
       </c>
       <c r="T35" s="1">
-        <v>-0.7218578311102668</v>
+        <v>8.6864156104181411E-2</v>
       </c>
       <c r="U35" s="1">
-        <v>-0.79308059445831791</v>
+        <v>0.12710133808296287</v>
       </c>
       <c r="V35" s="1">
-        <v>-0.77830574819028975</v>
+        <v>1.836431512714598E-2</v>
       </c>
       <c r="W35" s="1">
-        <v>-0.79304829728323867</v>
+        <v>-3.3742848828749672E-2</v>
       </c>
       <c r="X35" s="1">
-        <v>-0.1203094589467008</v>
+        <v>-2.1858999802256605E-2</v>
       </c>
       <c r="Y35" s="1">
-        <v>-0.13173541022504839</v>
+        <v>-3.6826859106653953E-3</v>
       </c>
       <c r="Z35" s="1">
-        <v>-0.15477999190839159</v>
+        <v>9.8322876457008213E-3</v>
       </c>
       <c r="AA35" s="1">
-        <v>-0.1377750642963369</v>
+        <v>-4.1063908730908372E-3</v>
       </c>
       <c r="AB35" s="1">
-        <v>0.176727313993676</v>
+        <v>4.2475290648051778E-2</v>
       </c>
       <c r="AC35" s="1">
-        <v>6.2611639792251594E-2</v>
+        <v>-4.5626095317895077E-2</v>
       </c>
       <c r="AD35" s="1">
-        <v>-0.1059329189807081</v>
+        <v>-1.7486716778097766E-2</v>
       </c>
       <c r="AE35" s="1">
-        <v>-0.14574799931140611</v>
+        <v>2.2226365118538149E-2</v>
       </c>
       <c r="AF35" s="1">
-        <v>-0.13435550836996879</v>
+        <v>-4.234654867208032E-3</v>
       </c>
       <c r="AG35" s="1">
-        <v>-0.16249423835184221</v>
+        <v>3.3821209334910118E-2</v>
       </c>
       <c r="AH35" s="1">
-        <v>-9.5143503848782895E-2</v>
+        <v>9.2650885080954509E-2</v>
       </c>
       <c r="AI35" s="1">
-        <v>-0.11343035991063991</v>
+        <v>-2.0717887566060078E-2</v>
       </c>
       <c r="AJ35" s="1">
-        <v>2.200100889858708</v>
+        <v>1.0253684423017821</v>
       </c>
     </row>
   </sheetData>
@@ -21623,14 +21639,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AJ35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="36" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -21740,7 +21756,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -21850,7 +21866,7 @@
         <v>-3.7814478253794997E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>93</v>
       </c>
@@ -21960,7 +21976,7 @@
         <v>-0.2074933419043116</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>79</v>
       </c>
@@ -22070,7 +22086,7 @@
         <v>-0.35953686251222211</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -22180,7 +22196,7 @@
         <v>-0.28699336309724982</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -22290,7 +22306,7 @@
         <v>-0.2405020523833559</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>81</v>
       </c>
@@ -22400,7 +22416,7 @@
         <v>-0.27260553871933058</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -22510,7 +22526,7 @@
         <v>-0.31015112380622151</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -22620,7 +22636,7 @@
         <v>1.26450822082663E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -22730,7 +22746,7 @@
         <v>-0.16728659744106911</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -22840,7 +22856,7 @@
         <v>-3.4040249556499702E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -22950,7 +22966,7 @@
         <v>6.8983958674303306E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -23060,7 +23076,7 @@
         <v>-8.6365688280253705E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -23170,7 +23186,7 @@
         <v>-9.2216637121189493E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -23280,7 +23296,7 @@
         <v>-9.1701780262554697E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -23390,7 +23406,7 @@
         <v>-0.1113977526877593</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -23500,7 +23516,7 @@
         <v>-0.1043666001851246</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -23610,7 +23626,7 @@
         <v>-9.5283964633768606E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -23720,7 +23736,7 @@
         <v>-9.5493526168155096E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -23830,7 +23846,7 @@
         <v>-0.10131411594730021</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -23940,7 +23956,7 @@
         <v>-0.1212549445862567</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -24050,7 +24066,7 @@
         <v>-0.1294223306990572</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -24160,7 +24176,7 @@
         <v>-4.9365851743387298E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -24270,7 +24286,7 @@
         <v>-0.13798300243353259</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -24380,7 +24396,7 @@
         <v>-8.0046060989929099E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -24490,7 +24506,7 @@
         <v>-8.5638707159970198E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -24600,7 +24616,7 @@
         <v>-0.10864118533795</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -24710,7 +24726,7 @@
         <v>-0.1118489837055773</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -24820,7 +24836,7 @@
         <v>-4.3711284829743201E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -24930,7 +24946,7 @@
         <v>-4.8131979733492002E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -25040,7 +25056,7 @@
         <v>-3.6480929500902197E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -25150,7 +25166,7 @@
         <v>1.3967757931692699E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -25260,7 +25276,7 @@
         <v>-4.8951957275511798E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -25370,7 +25386,7 @@
         <v>-7.2220769338407306E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -25488,14 +25504,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AE30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="31" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -25590,7 +25606,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -25685,7 +25701,7 @@
         <v>-3.1628627677060303E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -25780,7 +25796,7 @@
         <v>-9.6794186919319805E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -25875,7 +25891,7 @@
         <v>-2.3975199324354799E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -25970,7 +25986,7 @@
         <v>-7.2754322479982106E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -26065,7 +26081,7 @@
         <v>-4.9749374099907498E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -26160,7 +26176,7 @@
         <v>-5.7768528435868799E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -26255,7 +26271,7 @@
         <v>-1.7286159196759899E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -26350,7 +26366,7 @@
         <v>-4.5748797556291097E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -26445,7 +26461,7 @@
         <v>-3.897339329034E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -26540,7 +26556,7 @@
         <v>4.7923253744458202E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -26635,7 +26651,7 @@
         <v>-8.8597346434286697E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -26730,7 +26746,7 @@
         <v>-0.10050252779289311</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -26825,7 +26841,7 @@
         <v>-8.4223963051623399E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -26920,7 +26936,7 @@
         <v>-8.9758283309549006E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -27015,7 +27031,7 @@
         <v>-9.1086266970222304E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -27110,7 +27126,7 @@
         <v>-7.9538057523445393E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -27205,7 +27221,7 @@
         <v>-8.2826357026808295E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -27300,7 +27316,7 @@
         <v>-8.1305991543890593E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -27395,7 +27411,7 @@
         <v>-8.8848116631104299E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -27490,7 +27506,7 @@
         <v>-7.7112049195991406E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -27585,7 +27601,7 @@
         <v>-1.77071494746864E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -27680,7 +27696,7 @@
         <v>-2.83300092550423E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -27775,7 +27791,7 @@
         <v>-1.7661281059096999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -27870,7 +27886,7 @@
         <v>-1.79695878284536E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -27965,7 +27981,7 @@
         <v>-1.58598939762464E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -28060,7 +28076,7 @@
         <v>-1.39140898995178E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -28155,7 +28171,7 @@
         <v>-1.1406616043596499E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -28250,7 +28266,7 @@
         <v>3.6801411303322602E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -28353,14 +28369,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AO40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="41" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -28485,7 +28501,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -28610,7 +28626,7 @@
         <v>4.0433191816025249E-6</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -28735,7 +28751,7 @@
         <v>3.49592498304846E-6</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -28860,7 +28876,7 @@
         <v>-2.4427372752261261E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -28985,7 +29001,7 @@
         <v>-1.584097106073646E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -29110,7 +29126,7 @@
         <v>1.132991816790538E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -29235,7 +29251,7 @@
         <v>1.1323480226624141E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -29360,7 +29376,7 @@
         <v>1.911268337222125E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>87</v>
       </c>
@@ -29485,7 +29501,7 @@
         <v>1.1549264869059269E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>88</v>
       </c>
@@ -29610,7 +29626,7 @@
         <v>5.7381616084089552E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>89</v>
       </c>
@@ -29735,7 +29751,7 @@
         <v>1.374319999733432E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>90</v>
       </c>
@@ -29860,7 +29876,7 @@
         <v>3.7655461664934629E-6</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -29985,7 +30001,7 @@
         <v>-1.9334521281639851E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -30110,7 +30126,7 @@
         <v>-6.1633747065305896E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -30235,7 +30251,7 @@
         <v>-1.3879149665434921E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -30360,7 +30376,7 @@
         <v>-8.641944892795823E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -30485,7 +30501,7 @@
         <v>2.216961547663129E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -30610,7 +30626,7 @@
         <v>1.6775143114282962E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -30735,7 +30751,7 @@
         <v>6.9910489060675285E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -30860,7 +30876,7 @@
         <v>9.0394553169757534E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -30985,7 +31001,7 @@
         <v>-3.0685740368869051E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -31110,7 +31126,7 @@
         <v>1.1951967945188759E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -31235,7 +31251,7 @@
         <v>-8.6004566279602866E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -31360,7 +31376,7 @@
         <v>1.8780930698333569E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -31485,7 +31501,7 @@
         <v>-1.164798083938484E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -31610,7 +31626,7 @@
         <v>6.7382866370154307E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -31735,7 +31751,7 @@
         <v>-1.497240183044132E-5</v>
       </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -31860,7 +31876,7 @@
         <v>4.1997790806976989E-6</v>
       </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -31985,7 +32001,7 @@
         <v>5.1494756388390722E-5</v>
       </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -32110,7 +32126,7 @@
         <v>-3.67026898663178E-6</v>
       </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -32235,7 +32251,7 @@
         <v>4.1917300072169951E-5</v>
       </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -32360,7 +32376,7 @@
         <v>-8.5003342270408375E-6</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -32485,7 +32501,7 @@
         <v>-3.5809726366107177E-5</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -32610,7 +32626,7 @@
         <v>-3.4668844368864203E-5</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -32735,7 +32751,7 @@
         <v>-8.3820398844004163E-5</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -32860,7 +32876,7 @@
         <v>-8.6403363961086007E-5</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -32985,7 +33001,7 @@
         <v>-1.7163395892305571E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>35</v>
       </c>
@@ -33110,7 +33126,7 @@
         <v>-3.2671194093044492E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>36</v>
       </c>
@@ -33235,7 +33251,7 @@
         <v>-3.9990307093894376E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>95</v>
       </c>
